--- a/docs/samples/hisaar360-bulk-medicines-sample-100.xlsx
+++ b/docs/samples/hisaar360-bulk-medicines-sample-100.xlsx
@@ -3,8 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Medicines" sheetId="1" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -464,9 +463,9 @@
         <v>tablet</v>
       </c>
       <c r="C2" t="str">
-        <v>MED-001</v>
-      </c>
-      <c r="D2" t="str">
+        <v>SMP064345-001</v>
+      </c>
+      <c r="D2">
         <v>500</v>
       </c>
       <c r="E2" t="str">
@@ -476,7 +475,7 @@
         <v>Analgesics</v>
       </c>
       <c r="G2" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -487,29 +486,23 @@
       <c r="J2">
         <v>10</v>
       </c>
-      <c r="K2" t="str">
-        <v>8901100000001</v>
+      <c r="K2">
+        <v>89064345001</v>
       </c>
       <c r="L2" t="str">
-        <v>BCH-2026-001</v>
-      </c>
-      <c r="M2" t="str">
-        <v>2025-01-01</v>
-      </c>
-      <c r="N2" t="str">
-        <v>2027-01-04</v>
+        <v>B064345-001</v>
+      </c>
+      <c r="M2">
+        <v>45658.20847222222</v>
+      </c>
+      <c r="N2">
+        <v>46391.20847222222</v>
       </c>
       <c r="O2" t="str">
         <v>Getz</v>
       </c>
       <c r="P2" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R2">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="3">
@@ -520,9 +513,9 @@
         <v>capsule</v>
       </c>
       <c r="C3" t="str">
-        <v>MED-002</v>
-      </c>
-      <c r="D3" t="str">
+        <v>SMP064345-002</v>
+      </c>
+      <c r="D3">
         <v>250</v>
       </c>
       <c r="E3" t="str">
@@ -532,7 +525,7 @@
         <v>Antibiotics</v>
       </c>
       <c r="G3" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -543,29 +536,23 @@
       <c r="J3">
         <v>12</v>
       </c>
-      <c r="K3" t="str">
-        <v>8901100000002</v>
+      <c r="K3">
+        <v>89064345002</v>
       </c>
       <c r="L3" t="str">
-        <v>BCH-2026-002</v>
-      </c>
-      <c r="M3" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="N3" t="str">
-        <v>2029-02-05</v>
+        <v>B064345-002</v>
+      </c>
+      <c r="M3">
+        <v>46055.20847222222</v>
+      </c>
+      <c r="N3">
+        <v>47154.20847222222</v>
       </c>
       <c r="O3" t="str">
         <v>Searle</v>
       </c>
       <c r="P3" t="str">
         <v>No</v>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -576,9 +563,9 @@
         <v>capsule</v>
       </c>
       <c r="C4" t="str">
-        <v>MED-003</v>
-      </c>
-      <c r="D4" t="str">
+        <v>SMP064345-003</v>
+      </c>
+      <c r="D4">
         <v>500</v>
       </c>
       <c r="E4" t="str">
@@ -588,7 +575,7 @@
         <v>Antihistamines</v>
       </c>
       <c r="G4" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H4">
         <v>11</v>
@@ -599,29 +586,23 @@
       <c r="J4">
         <v>14</v>
       </c>
-      <c r="K4" t="str">
-        <v>8901100000003</v>
+      <c r="K4">
+        <v>89064345003</v>
       </c>
       <c r="L4" t="str">
-        <v>BCH-2026-003</v>
-      </c>
-      <c r="M4" t="str">
-        <v>2025-03-03</v>
-      </c>
-      <c r="N4" t="str">
-        <v>2027-03-06</v>
+        <v>B064345-003</v>
+      </c>
+      <c r="M4">
+        <v>45719.20847222222</v>
+      </c>
+      <c r="N4">
+        <v>46452.20847222222</v>
       </c>
       <c r="O4" t="str">
         <v>GSK</v>
       </c>
       <c r="P4" t="str">
         <v>No</v>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
-      </c>
-      <c r="R4" t="str">
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -632,9 +613,9 @@
         <v>tablet</v>
       </c>
       <c r="C5" t="str">
-        <v>MED-004</v>
-      </c>
-      <c r="D5" t="str">
+        <v>SMP064345-004</v>
+      </c>
+      <c r="D5">
         <v>10</v>
       </c>
       <c r="E5" t="str">
@@ -644,7 +625,7 @@
         <v>Antacids</v>
       </c>
       <c r="G5" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H5">
         <v>14</v>
@@ -655,29 +636,23 @@
       <c r="J5">
         <v>16</v>
       </c>
-      <c r="K5" t="str">
-        <v>8901100000004</v>
+      <c r="K5">
+        <v>89064345004</v>
       </c>
       <c r="L5" t="str">
-        <v>BCH-2026-004</v>
-      </c>
-      <c r="M5" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="N5" t="str">
-        <v>2029-04-07</v>
+        <v>B064345-004</v>
+      </c>
+      <c r="M5">
+        <v>46116.20847222222</v>
+      </c>
+      <c r="N5">
+        <v>47215.20847222222</v>
       </c>
       <c r="O5" t="str">
         <v>Abbott</v>
       </c>
       <c r="P5" t="str">
         <v>No</v>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-      <c r="R5" t="str">
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -688,9 +663,9 @@
         <v>capsule</v>
       </c>
       <c r="C6" t="str">
-        <v>MED-005</v>
-      </c>
-      <c r="D6" t="str">
+        <v>SMP064345-005</v>
+      </c>
+      <c r="D6">
         <v>20</v>
       </c>
       <c r="E6" t="str">
@@ -700,7 +675,7 @@
         <v>Cardiovascular</v>
       </c>
       <c r="G6" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H6">
         <v>17</v>
@@ -711,29 +686,23 @@
       <c r="J6">
         <v>18</v>
       </c>
-      <c r="K6" t="str">
-        <v>8901100000005</v>
+      <c r="K6">
+        <v>89064345005</v>
       </c>
       <c r="L6" t="str">
-        <v>BCH-2026-005</v>
-      </c>
-      <c r="M6" t="str">
-        <v>2025-05-05</v>
-      </c>
-      <c r="N6" t="str">
-        <v>2027-05-08</v>
+        <v>B064345-005</v>
+      </c>
+      <c r="M6">
+        <v>45782.20847222222</v>
+      </c>
+      <c r="N6">
+        <v>46515.20847222222</v>
       </c>
       <c r="O6" t="str">
         <v>Hilton</v>
       </c>
       <c r="P6" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R6">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="7">
@@ -744,9 +713,9 @@
         <v>tablet</v>
       </c>
       <c r="C7" t="str">
-        <v>MED-006</v>
-      </c>
-      <c r="D7" t="str">
+        <v>SMP064345-006</v>
+      </c>
+      <c r="D7">
         <v>500</v>
       </c>
       <c r="E7" t="str">
@@ -756,7 +725,7 @@
         <v>Diabetes</v>
       </c>
       <c r="G7" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H7">
         <v>20</v>
@@ -767,29 +736,23 @@
       <c r="J7">
         <v>20</v>
       </c>
-      <c r="K7" t="str">
-        <v>8901100000006</v>
+      <c r="K7">
+        <v>89064345006</v>
       </c>
       <c r="L7" t="str">
-        <v>BCH-2026-006</v>
-      </c>
-      <c r="M7" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="N7" t="str">
-        <v>2029-06-09</v>
+        <v>B064345-006</v>
+      </c>
+      <c r="M7">
+        <v>46179.20847222222</v>
+      </c>
+      <c r="N7">
+        <v>47278.20847222222</v>
       </c>
       <c r="O7" t="str">
         <v>Sami</v>
       </c>
       <c r="P7" t="str">
         <v>No</v>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
-      <c r="R7" t="str">
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -800,9 +763,9 @@
         <v>tablet</v>
       </c>
       <c r="C8" t="str">
-        <v>MED-007</v>
-      </c>
-      <c r="D8" t="str">
+        <v>SMP064345-007</v>
+      </c>
+      <c r="D8">
         <v>500</v>
       </c>
       <c r="E8" t="str">
@@ -812,7 +775,7 @@
         <v>Vitamins</v>
       </c>
       <c r="G8" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H8">
         <v>23</v>
@@ -823,29 +786,23 @@
       <c r="J8">
         <v>22</v>
       </c>
-      <c r="K8" t="str">
-        <v>8901100000007</v>
+      <c r="K8">
+        <v>89064345007</v>
       </c>
       <c r="L8" t="str">
-        <v>BCH-2026-007</v>
-      </c>
-      <c r="M8" t="str">
-        <v>2025-07-07</v>
-      </c>
-      <c r="N8" t="str">
-        <v>2027-07-10</v>
+        <v>B064345-007</v>
+      </c>
+      <c r="M8">
+        <v>45845.20847222222</v>
+      </c>
+      <c r="N8">
+        <v>46578.20847222222</v>
       </c>
       <c r="O8" t="str">
         <v>Highnoon</v>
       </c>
       <c r="P8" t="str">
         <v>No</v>
-      </c>
-      <c r="Q8" t="str">
-        <v/>
-      </c>
-      <c r="R8" t="str">
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -856,9 +813,9 @@
         <v>tablet</v>
       </c>
       <c r="C9" t="str">
-        <v>MED-008</v>
-      </c>
-      <c r="D9" t="str">
+        <v>SMP064345-008</v>
+      </c>
+      <c r="D9">
         <v>850</v>
       </c>
       <c r="E9" t="str">
@@ -868,7 +825,7 @@
         <v>Respiratory</v>
       </c>
       <c r="G9" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H9">
         <v>22.5</v>
@@ -879,29 +836,23 @@
       <c r="J9">
         <v>24</v>
       </c>
-      <c r="K9" t="str">
-        <v>8901100000008</v>
+      <c r="K9">
+        <v>89064345008</v>
       </c>
       <c r="L9" t="str">
-        <v>BCH-2026-008</v>
-      </c>
-      <c r="M9" t="str">
-        <v>2026-08-08</v>
-      </c>
-      <c r="N9" t="str">
-        <v>2029-08-11</v>
+        <v>B064345-008</v>
+      </c>
+      <c r="M9">
+        <v>46242.20847222222</v>
+      </c>
+      <c r="N9">
+        <v>47341.20847222222</v>
       </c>
       <c r="O9" t="str">
         <v>Martin Dow</v>
       </c>
       <c r="P9" t="str">
         <v>No</v>
-      </c>
-      <c r="Q9" t="str">
-        <v/>
-      </c>
-      <c r="R9" t="str">
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -912,9 +863,9 @@
         <v>tablet</v>
       </c>
       <c r="C10" t="str">
-        <v>MED-009</v>
-      </c>
-      <c r="D10" t="str">
+        <v>SMP064345-009</v>
+      </c>
+      <c r="D10">
         <v>5</v>
       </c>
       <c r="E10" t="str">
@@ -924,7 +875,7 @@
         <v>Dermatology</v>
       </c>
       <c r="G10" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H10">
         <v>25.5</v>
@@ -935,29 +886,23 @@
       <c r="J10">
         <v>26</v>
       </c>
-      <c r="K10" t="str">
-        <v>8901100000009</v>
+      <c r="K10">
+        <v>89064345009</v>
       </c>
       <c r="L10" t="str">
-        <v>BCH-2026-009</v>
-      </c>
-      <c r="M10" t="str">
-        <v>2025-09-09</v>
-      </c>
-      <c r="N10" t="str">
-        <v>2027-09-12</v>
+        <v>B064345-009</v>
+      </c>
+      <c r="M10">
+        <v>45909.20847222222</v>
+      </c>
+      <c r="N10">
+        <v>46642.20847222222</v>
       </c>
       <c r="O10" t="str">
         <v>Pfizer</v>
       </c>
       <c r="P10" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R10">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="11">
@@ -968,9 +913,9 @@
         <v>tablet</v>
       </c>
       <c r="C11" t="str">
-        <v>MED-010</v>
-      </c>
-      <c r="D11" t="str">
+        <v>SMP064345-010</v>
+      </c>
+      <c r="D11">
         <v>10</v>
       </c>
       <c r="E11" t="str">
@@ -980,7 +925,7 @@
         <v>Injectables</v>
       </c>
       <c r="G11" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H11">
         <v>28.5</v>
@@ -991,29 +936,23 @@
       <c r="J11">
         <v>28</v>
       </c>
-      <c r="K11" t="str">
-        <v>8901100000010</v>
+      <c r="K11">
+        <v>89064345010</v>
       </c>
       <c r="L11" t="str">
-        <v>BCH-2026-010</v>
-      </c>
-      <c r="M11" t="str">
-        <v>2026-10-10</v>
-      </c>
-      <c r="N11" t="str">
-        <v>2029-10-13</v>
+        <v>B064345-010</v>
+      </c>
+      <c r="M11">
+        <v>46305.20847222222</v>
+      </c>
+      <c r="N11">
+        <v>47404.20847222222</v>
       </c>
       <c r="O11" t="str">
         <v>Novartis</v>
       </c>
       <c r="P11" t="str">
         <v>No</v>
-      </c>
-      <c r="Q11" t="str">
-        <v/>
-      </c>
-      <c r="R11" t="str">
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -1024,9 +963,9 @@
         <v>tablet</v>
       </c>
       <c r="C12" t="str">
-        <v>MED-011</v>
-      </c>
-      <c r="D12" t="str">
+        <v>SMP064345-011</v>
+      </c>
+      <c r="D12">
         <v>10</v>
       </c>
       <c r="E12" t="str">
@@ -1036,7 +975,7 @@
         <v>Analgesics</v>
       </c>
       <c r="G12" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H12">
         <v>31.5</v>
@@ -1047,29 +986,23 @@
       <c r="J12">
         <v>30</v>
       </c>
-      <c r="K12" t="str">
-        <v>8901100000011</v>
+      <c r="K12">
+        <v>89064345011</v>
       </c>
       <c r="L12" t="str">
-        <v>BCH-2026-011</v>
-      </c>
-      <c r="M12" t="str">
-        <v>2025-11-11</v>
-      </c>
-      <c r="N12" t="str">
-        <v>2027-11-14</v>
+        <v>B064345-011</v>
+      </c>
+      <c r="M12">
+        <v>45972.20847222222</v>
+      </c>
+      <c r="N12">
+        <v>46705.20847222222</v>
       </c>
       <c r="O12" t="str">
         <v>Generic</v>
       </c>
       <c r="P12" t="str">
         <v>No</v>
-      </c>
-      <c r="Q12" t="str">
-        <v/>
-      </c>
-      <c r="R12" t="str">
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -1080,9 +1013,9 @@
         <v>tablet</v>
       </c>
       <c r="C13" t="str">
-        <v>MED-012</v>
-      </c>
-      <c r="D13" t="str">
+        <v>SMP064345-012</v>
+      </c>
+      <c r="D13">
         <v>20</v>
       </c>
       <c r="E13" t="str">
@@ -1092,7 +1025,7 @@
         <v>Antibiotics</v>
       </c>
       <c r="G13" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H13">
         <v>34.5</v>
@@ -1103,29 +1036,23 @@
       <c r="J13">
         <v>32</v>
       </c>
-      <c r="K13" t="str">
-        <v>8901100000012</v>
+      <c r="K13">
+        <v>89064345012</v>
       </c>
       <c r="L13" t="str">
-        <v>BCH-2026-012</v>
-      </c>
-      <c r="M13" t="str">
-        <v>2026-12-12</v>
-      </c>
-      <c r="N13" t="str">
-        <v>2029-12-15</v>
+        <v>B064345-012</v>
+      </c>
+      <c r="M13">
+        <v>46368.20847222222</v>
+      </c>
+      <c r="N13">
+        <v>47467.20847222222</v>
       </c>
       <c r="O13" t="str">
         <v>Getz</v>
       </c>
       <c r="P13" t="str">
         <v>No</v>
-      </c>
-      <c r="Q13" t="str">
-        <v/>
-      </c>
-      <c r="R13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -1136,9 +1063,9 @@
         <v>tablet</v>
       </c>
       <c r="C14" t="str">
-        <v>MED-013</v>
-      </c>
-      <c r="D14" t="str">
+        <v>SMP064345-013</v>
+      </c>
+      <c r="D14">
         <v>50</v>
       </c>
       <c r="E14" t="str">
@@ -1148,7 +1075,7 @@
         <v>Antihistamines</v>
       </c>
       <c r="G14" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H14">
         <v>37.5</v>
@@ -1159,29 +1086,23 @@
       <c r="J14">
         <v>34</v>
       </c>
-      <c r="K14" t="str">
-        <v>8901100000013</v>
+      <c r="K14">
+        <v>89064345013</v>
       </c>
       <c r="L14" t="str">
-        <v>BCH-2026-013</v>
-      </c>
-      <c r="M14" t="str">
-        <v>2025-01-13</v>
-      </c>
-      <c r="N14" t="str">
-        <v>2027-01-16</v>
+        <v>B064345-013</v>
+      </c>
+      <c r="M14">
+        <v>45670.20847222222</v>
+      </c>
+      <c r="N14">
+        <v>46403.20847222222</v>
       </c>
       <c r="O14" t="str">
         <v>Searle</v>
       </c>
       <c r="P14" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q14" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R14">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="15">
@@ -1192,9 +1113,9 @@
         <v>tablet</v>
       </c>
       <c r="C15" t="str">
-        <v>MED-014</v>
-      </c>
-      <c r="D15" t="str">
+        <v>SMP064345-014</v>
+      </c>
+      <c r="D15">
         <v>100</v>
       </c>
       <c r="E15" t="str">
@@ -1204,7 +1125,7 @@
         <v>Antacids</v>
       </c>
       <c r="G15" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H15">
         <v>40.5</v>
@@ -1215,29 +1136,23 @@
       <c r="J15">
         <v>36</v>
       </c>
-      <c r="K15" t="str">
-        <v>8901100000014</v>
+      <c r="K15">
+        <v>89064345014</v>
       </c>
       <c r="L15" t="str">
-        <v>BCH-2026-014</v>
-      </c>
-      <c r="M15" t="str">
-        <v>2026-02-14</v>
-      </c>
-      <c r="N15" t="str">
-        <v>2029-02-17</v>
+        <v>B064345-014</v>
+      </c>
+      <c r="M15">
+        <v>46067.20847222222</v>
+      </c>
+      <c r="N15">
+        <v>47166.20847222222</v>
       </c>
       <c r="O15" t="str">
         <v>GSK</v>
       </c>
       <c r="P15" t="str">
         <v>No</v>
-      </c>
-      <c r="Q15" t="str">
-        <v/>
-      </c>
-      <c r="R15" t="str">
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -1248,9 +1163,9 @@
         <v>tablet</v>
       </c>
       <c r="C16" t="str">
-        <v>MED-015</v>
-      </c>
-      <c r="D16" t="str">
+        <v>SMP064345-015</v>
+      </c>
+      <c r="D16">
         <v>400</v>
       </c>
       <c r="E16" t="str">
@@ -1260,7 +1175,7 @@
         <v>Cardiovascular</v>
       </c>
       <c r="G16" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H16">
         <v>40</v>
@@ -1271,29 +1186,23 @@
       <c r="J16">
         <v>38</v>
       </c>
-      <c r="K16" t="str">
-        <v>8901100000015</v>
+      <c r="K16">
+        <v>89064345015</v>
       </c>
       <c r="L16" t="str">
-        <v>BCH-2026-015</v>
-      </c>
-      <c r="M16" t="str">
-        <v>2025-03-15</v>
-      </c>
-      <c r="N16" t="str">
-        <v>2027-03-18</v>
+        <v>B064345-015</v>
+      </c>
+      <c r="M16">
+        <v>45731.20847222222</v>
+      </c>
+      <c r="N16">
+        <v>46464.20847222222</v>
       </c>
       <c r="O16" t="str">
         <v>Abbott</v>
       </c>
       <c r="P16" t="str">
         <v>No</v>
-      </c>
-      <c r="Q16" t="str">
-        <v/>
-      </c>
-      <c r="R16" t="str">
-        <v/>
       </c>
     </row>
     <row r="17">
@@ -1304,9 +1213,9 @@
         <v>tablet</v>
       </c>
       <c r="C17" t="str">
-        <v>MED-016</v>
-      </c>
-      <c r="D17" t="str">
+        <v>SMP064345-016</v>
+      </c>
+      <c r="D17">
         <v>50</v>
       </c>
       <c r="E17" t="str">
@@ -1316,7 +1225,7 @@
         <v>Diabetes</v>
       </c>
       <c r="G17" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H17">
         <v>43</v>
@@ -1327,29 +1236,23 @@
       <c r="J17">
         <v>40</v>
       </c>
-      <c r="K17" t="str">
-        <v>8901100000016</v>
+      <c r="K17">
+        <v>89064345016</v>
       </c>
       <c r="L17" t="str">
-        <v>BCH-2026-016</v>
-      </c>
-      <c r="M17" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="N17" t="str">
-        <v>2029-04-19</v>
+        <v>B064345-016</v>
+      </c>
+      <c r="M17">
+        <v>46128.20847222222</v>
+      </c>
+      <c r="N17">
+        <v>47227.20847222222</v>
       </c>
       <c r="O17" t="str">
         <v>Hilton</v>
       </c>
       <c r="P17" t="str">
         <v>No</v>
-      </c>
-      <c r="Q17" t="str">
-        <v/>
-      </c>
-      <c r="R17" t="str">
-        <v/>
       </c>
     </row>
     <row r="18">
@@ -1360,9 +1263,9 @@
         <v>tablet</v>
       </c>
       <c r="C18" t="str">
-        <v>MED-017</v>
-      </c>
-      <c r="D18" t="str">
+        <v>SMP064345-017</v>
+      </c>
+      <c r="D18">
         <v>500</v>
       </c>
       <c r="E18" t="str">
@@ -1372,7 +1275,7 @@
         <v>Vitamins</v>
       </c>
       <c r="G18" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H18">
         <v>46</v>
@@ -1383,29 +1286,23 @@
       <c r="J18">
         <v>42</v>
       </c>
-      <c r="K18" t="str">
-        <v>8901100000017</v>
+      <c r="K18">
+        <v>89064345017</v>
       </c>
       <c r="L18" t="str">
-        <v>BCH-2026-017</v>
-      </c>
-      <c r="M18" t="str">
-        <v>2025-05-17</v>
-      </c>
-      <c r="N18" t="str">
-        <v>2027-05-20</v>
+        <v>B064345-017</v>
+      </c>
+      <c r="M18">
+        <v>45794.20847222222</v>
+      </c>
+      <c r="N18">
+        <v>46527.20847222222</v>
       </c>
       <c r="O18" t="str">
         <v>Sami</v>
       </c>
       <c r="P18" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q18" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R18">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="19">
@@ -1416,9 +1313,9 @@
         <v>tablet</v>
       </c>
       <c r="C19" t="str">
-        <v>MED-018</v>
-      </c>
-      <c r="D19" t="str">
+        <v>SMP064345-018</v>
+      </c>
+      <c r="D19">
         <v>500</v>
       </c>
       <c r="E19" t="str">
@@ -1428,7 +1325,7 @@
         <v>Respiratory</v>
       </c>
       <c r="G19" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H19">
         <v>49</v>
@@ -1439,29 +1336,23 @@
       <c r="J19">
         <v>44</v>
       </c>
-      <c r="K19" t="str">
-        <v>8901100000018</v>
+      <c r="K19">
+        <v>89064345018</v>
       </c>
       <c r="L19" t="str">
-        <v>BCH-2026-018</v>
-      </c>
-      <c r="M19" t="str">
-        <v>2026-06-18</v>
-      </c>
-      <c r="N19" t="str">
-        <v>2029-06-21</v>
+        <v>B064345-018</v>
+      </c>
+      <c r="M19">
+        <v>46191.20847222222</v>
+      </c>
+      <c r="N19">
+        <v>47290.20847222222</v>
       </c>
       <c r="O19" t="str">
         <v>Highnoon</v>
       </c>
       <c r="P19" t="str">
         <v>No</v>
-      </c>
-      <c r="Q19" t="str">
-        <v/>
-      </c>
-      <c r="R19" t="str">
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -1472,9 +1363,9 @@
         <v>tablet</v>
       </c>
       <c r="C20" t="str">
-        <v>MED-019</v>
-      </c>
-      <c r="D20" t="str">
+        <v>SMP064345-019</v>
+      </c>
+      <c r="D20">
         <v>250</v>
       </c>
       <c r="E20" t="str">
@@ -1484,7 +1375,7 @@
         <v>Dermatology</v>
       </c>
       <c r="G20" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H20">
         <v>52</v>
@@ -1495,29 +1386,23 @@
       <c r="J20">
         <v>46</v>
       </c>
-      <c r="K20" t="str">
-        <v>8901100000019</v>
+      <c r="K20">
+        <v>89064345019</v>
       </c>
       <c r="L20" t="str">
-        <v>BCH-2026-019</v>
-      </c>
-      <c r="M20" t="str">
-        <v>2025-07-19</v>
-      </c>
-      <c r="N20" t="str">
-        <v>2027-07-22</v>
+        <v>B064345-019</v>
+      </c>
+      <c r="M20">
+        <v>45857.20847222222</v>
+      </c>
+      <c r="N20">
+        <v>46590.20847222222</v>
       </c>
       <c r="O20" t="str">
         <v>Martin Dow</v>
       </c>
       <c r="P20" t="str">
         <v>No</v>
-      </c>
-      <c r="Q20" t="str">
-        <v/>
-      </c>
-      <c r="R20" t="str">
-        <v/>
       </c>
     </row>
     <row r="21">
@@ -1528,9 +1413,9 @@
         <v>capsule</v>
       </c>
       <c r="C21" t="str">
-        <v>MED-020</v>
-      </c>
-      <c r="D21" t="str">
+        <v>SMP064345-020</v>
+      </c>
+      <c r="D21">
         <v>100</v>
       </c>
       <c r="E21" t="str">
@@ -1540,7 +1425,7 @@
         <v>Injectables</v>
       </c>
       <c r="G21" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H21">
         <v>55</v>
@@ -1551,29 +1436,23 @@
       <c r="J21">
         <v>48</v>
       </c>
-      <c r="K21" t="str">
-        <v>8901100000020</v>
+      <c r="K21">
+        <v>89064345020</v>
       </c>
       <c r="L21" t="str">
-        <v>BCH-2026-020</v>
-      </c>
-      <c r="M21" t="str">
-        <v>2026-08-20</v>
-      </c>
-      <c r="N21" t="str">
-        <v>2029-08-23</v>
+        <v>B064345-020</v>
+      </c>
+      <c r="M21">
+        <v>46254.20847222222</v>
+      </c>
+      <c r="N21">
+        <v>47353.20847222222</v>
       </c>
       <c r="O21" t="str">
         <v>Pfizer</v>
       </c>
       <c r="P21" t="str">
         <v>No</v>
-      </c>
-      <c r="Q21" t="str">
-        <v/>
-      </c>
-      <c r="R21" t="str">
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -1584,9 +1463,9 @@
         <v>tablet</v>
       </c>
       <c r="C22" t="str">
-        <v>MED-021</v>
-      </c>
-      <c r="D22" t="str">
+        <v>SMP064345-021</v>
+      </c>
+      <c r="D22">
         <v>40</v>
       </c>
       <c r="E22" t="str">
@@ -1596,7 +1475,7 @@
         <v>Analgesics</v>
       </c>
       <c r="G22" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H22">
         <v>58</v>
@@ -1607,29 +1486,23 @@
       <c r="J22">
         <v>50</v>
       </c>
-      <c r="K22" t="str">
-        <v>8901100000021</v>
+      <c r="K22">
+        <v>89064345021</v>
       </c>
       <c r="L22" t="str">
-        <v>BCH-2026-021</v>
-      </c>
-      <c r="M22" t="str">
-        <v>2025-09-21</v>
-      </c>
-      <c r="N22" t="str">
-        <v>2027-09-24</v>
+        <v>B064345-021</v>
+      </c>
+      <c r="M22">
+        <v>45921.20847222222</v>
+      </c>
+      <c r="N22">
+        <v>46654.20847222222</v>
       </c>
       <c r="O22" t="str">
         <v>Novartis</v>
       </c>
       <c r="P22" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q22" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R22">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="23">
@@ -1640,9 +1513,9 @@
         <v>capsule</v>
       </c>
       <c r="C23" t="str">
-        <v>MED-022</v>
-      </c>
-      <c r="D23" t="str">
+        <v>SMP064345-022</v>
+      </c>
+      <c r="D23">
         <v>40</v>
       </c>
       <c r="E23" t="str">
@@ -1652,7 +1525,7 @@
         <v>Antibiotics</v>
       </c>
       <c r="G23" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H23">
         <v>57.5</v>
@@ -1663,29 +1536,23 @@
       <c r="J23">
         <v>52</v>
       </c>
-      <c r="K23" t="str">
-        <v>8901100000022</v>
+      <c r="K23">
+        <v>89064345022</v>
       </c>
       <c r="L23" t="str">
-        <v>BCH-2026-022</v>
-      </c>
-      <c r="M23" t="str">
-        <v>2026-10-22</v>
-      </c>
-      <c r="N23" t="str">
-        <v>2029-10-25</v>
+        <v>B064345-022</v>
+      </c>
+      <c r="M23">
+        <v>46317.20847222222</v>
+      </c>
+      <c r="N23">
+        <v>47416.20847222222</v>
       </c>
       <c r="O23" t="str">
         <v>Generic</v>
       </c>
       <c r="P23" t="str">
         <v>No</v>
-      </c>
-      <c r="Q23" t="str">
-        <v/>
-      </c>
-      <c r="R23" t="str">
-        <v/>
       </c>
     </row>
     <row r="24">
@@ -1696,9 +1563,9 @@
         <v>tablet</v>
       </c>
       <c r="C24" t="str">
-        <v>MED-023</v>
-      </c>
-      <c r="D24" t="str">
+        <v>SMP064345-023</v>
+      </c>
+      <c r="D24">
         <v>150</v>
       </c>
       <c r="E24" t="str">
@@ -1708,7 +1575,7 @@
         <v>Antihistamines</v>
       </c>
       <c r="G24" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H24">
         <v>60.5</v>
@@ -1719,29 +1586,23 @@
       <c r="J24">
         <v>54</v>
       </c>
-      <c r="K24" t="str">
-        <v>8901100000023</v>
+      <c r="K24">
+        <v>89064345023</v>
       </c>
       <c r="L24" t="str">
-        <v>BCH-2026-023</v>
-      </c>
-      <c r="M24" t="str">
-        <v>2025-11-23</v>
-      </c>
-      <c r="N24" t="str">
-        <v>2027-11-26</v>
+        <v>B064345-023</v>
+      </c>
+      <c r="M24">
+        <v>45984.20847222222</v>
+      </c>
+      <c r="N24">
+        <v>46717.20847222222</v>
       </c>
       <c r="O24" t="str">
         <v>Getz</v>
       </c>
       <c r="P24" t="str">
         <v>No</v>
-      </c>
-      <c r="Q24" t="str">
-        <v/>
-      </c>
-      <c r="R24" t="str">
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -1752,9 +1613,9 @@
         <v>tablet</v>
       </c>
       <c r="C25" t="str">
-        <v>MED-024</v>
-      </c>
-      <c r="D25" t="str">
+        <v>SMP064345-024</v>
+      </c>
+      <c r="D25">
         <v>10</v>
       </c>
       <c r="E25" t="str">
@@ -1764,7 +1625,7 @@
         <v>Antacids</v>
       </c>
       <c r="G25" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H25">
         <v>63.5</v>
@@ -1775,29 +1636,23 @@
       <c r="J25">
         <v>56</v>
       </c>
-      <c r="K25" t="str">
-        <v>8901100000024</v>
+      <c r="K25">
+        <v>89064345024</v>
       </c>
       <c r="L25" t="str">
-        <v>BCH-2026-024</v>
-      </c>
-      <c r="M25" t="str">
-        <v>2026-12-24</v>
-      </c>
-      <c r="N25" t="str">
-        <v>2029-12-27</v>
+        <v>B064345-024</v>
+      </c>
+      <c r="M25">
+        <v>46380.20847222222</v>
+      </c>
+      <c r="N25">
+        <v>47479.20847222222</v>
       </c>
       <c r="O25" t="str">
         <v>Searle</v>
       </c>
       <c r="P25" t="str">
         <v>No</v>
-      </c>
-      <c r="Q25" t="str">
-        <v/>
-      </c>
-      <c r="R25" t="str">
-        <v/>
       </c>
     </row>
     <row r="26">
@@ -1808,9 +1663,9 @@
         <v>tablet</v>
       </c>
       <c r="C26" t="str">
-        <v>MED-025</v>
-      </c>
-      <c r="D26" t="str">
+        <v>SMP064345-025</v>
+      </c>
+      <c r="D26">
         <v>8</v>
       </c>
       <c r="E26" t="str">
@@ -1820,7 +1675,7 @@
         <v>Cardiovascular</v>
       </c>
       <c r="G26" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H26">
         <v>66.5</v>
@@ -1831,29 +1686,23 @@
       <c r="J26">
         <v>58</v>
       </c>
-      <c r="K26" t="str">
-        <v>8901100000025</v>
+      <c r="K26">
+        <v>89064345025</v>
       </c>
       <c r="L26" t="str">
-        <v>BCH-2026-025</v>
-      </c>
-      <c r="M26" t="str">
-        <v>2025-01-25</v>
-      </c>
-      <c r="N26" t="str">
-        <v>2027-01-28</v>
+        <v>B064345-025</v>
+      </c>
+      <c r="M26">
+        <v>45682.20847222222</v>
+      </c>
+      <c r="N26">
+        <v>46415.20847222222</v>
       </c>
       <c r="O26" t="str">
         <v>GSK</v>
       </c>
       <c r="P26" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q26" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R26">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="27">
@@ -1864,9 +1713,9 @@
         <v>tablet</v>
       </c>
       <c r="C27" t="str">
-        <v>MED-026</v>
-      </c>
-      <c r="D27" t="str">
+        <v>SMP064345-026</v>
+      </c>
+      <c r="D27">
         <v>10</v>
       </c>
       <c r="E27" t="str">
@@ -1876,7 +1725,7 @@
         <v>Diabetes</v>
       </c>
       <c r="G27" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H27">
         <v>69.5</v>
@@ -1887,29 +1736,23 @@
       <c r="J27">
         <v>60</v>
       </c>
-      <c r="K27" t="str">
-        <v>8901100000026</v>
+      <c r="K27">
+        <v>89064345026</v>
       </c>
       <c r="L27" t="str">
-        <v>BCH-2026-026</v>
-      </c>
-      <c r="M27" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="N27" t="str">
-        <v>2029-02-28</v>
+        <v>B064345-026</v>
+      </c>
+      <c r="M27">
+        <v>46079.20847222222</v>
+      </c>
+      <c r="N27">
+        <v>47177.20847222222</v>
       </c>
       <c r="O27" t="str">
         <v>Abbott</v>
       </c>
       <c r="P27" t="str">
         <v>No</v>
-      </c>
-      <c r="Q27" t="str">
-        <v/>
-      </c>
-      <c r="R27" t="str">
-        <v/>
       </c>
     </row>
     <row r="28">
@@ -1920,9 +1763,9 @@
         <v>inhaler</v>
       </c>
       <c r="C28" t="str">
-        <v>MED-027</v>
-      </c>
-      <c r="D28" t="str">
+        <v>SMP064345-027</v>
+      </c>
+      <c r="D28">
         <v>100</v>
       </c>
       <c r="E28" t="str">
@@ -1932,7 +1775,7 @@
         <v>Vitamins</v>
       </c>
       <c r="G28" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H28">
         <v>72.5</v>
@@ -1943,29 +1786,23 @@
       <c r="J28">
         <v>62</v>
       </c>
-      <c r="K28" t="str">
-        <v>8901100000027</v>
+      <c r="K28">
+        <v>89064345027</v>
       </c>
       <c r="L28" t="str">
-        <v>BCH-2026-027</v>
-      </c>
-      <c r="M28" t="str">
-        <v>2025-03-27</v>
-      </c>
-      <c r="N28" t="str">
-        <v>2027-03-28</v>
+        <v>B064345-027</v>
+      </c>
+      <c r="M28">
+        <v>45743.20847222222</v>
+      </c>
+      <c r="N28">
+        <v>46474.20847222222</v>
       </c>
       <c r="O28" t="str">
         <v>Hilton</v>
       </c>
       <c r="P28" t="str">
         <v>No</v>
-      </c>
-      <c r="Q28" t="str">
-        <v/>
-      </c>
-      <c r="R28" t="str">
-        <v/>
       </c>
     </row>
     <row r="29">
@@ -1976,9 +1813,9 @@
         <v>inhaler</v>
       </c>
       <c r="C29" t="str">
-        <v>MED-028</v>
-      </c>
-      <c r="D29" t="str">
+        <v>SMP064345-028</v>
+      </c>
+      <c r="D29">
         <v>200</v>
       </c>
       <c r="E29" t="str">
@@ -1988,7 +1825,7 @@
         <v>Respiratory</v>
       </c>
       <c r="G29" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H29">
         <v>75.5</v>
@@ -1999,29 +1836,23 @@
       <c r="J29">
         <v>64</v>
       </c>
-      <c r="K29" t="str">
-        <v>8901100000028</v>
+      <c r="K29">
+        <v>89064345028</v>
       </c>
       <c r="L29" t="str">
-        <v>BCH-2026-028</v>
-      </c>
-      <c r="M29" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="N29" t="str">
-        <v>2029-04-04</v>
+        <v>B064345-028</v>
+      </c>
+      <c r="M29">
+        <v>46113.20847222222</v>
+      </c>
+      <c r="N29">
+        <v>47212.20847222222</v>
       </c>
       <c r="O29" t="str">
         <v>Sami</v>
       </c>
       <c r="P29" t="str">
         <v>No</v>
-      </c>
-      <c r="Q29" t="str">
-        <v/>
-      </c>
-      <c r="R29" t="str">
-        <v/>
       </c>
     </row>
     <row r="30">
@@ -2032,9 +1863,9 @@
         <v>tablet</v>
       </c>
       <c r="C30" t="str">
-        <v>MED-029</v>
-      </c>
-      <c r="D30" t="str">
+        <v>SMP064345-029</v>
+      </c>
+      <c r="D30">
         <v>10</v>
       </c>
       <c r="E30" t="str">
@@ -2044,7 +1875,7 @@
         <v>Dermatology</v>
       </c>
       <c r="G30" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H30">
         <v>75</v>
@@ -2055,29 +1886,23 @@
       <c r="J30">
         <v>66</v>
       </c>
-      <c r="K30" t="str">
-        <v>8901100000029</v>
+      <c r="K30">
+        <v>89064345029</v>
       </c>
       <c r="L30" t="str">
-        <v>BCH-2026-029</v>
-      </c>
-      <c r="M30" t="str">
-        <v>2025-05-02</v>
-      </c>
-      <c r="N30" t="str">
-        <v>2027-05-05</v>
+        <v>B064345-029</v>
+      </c>
+      <c r="M30">
+        <v>45779.20847222222</v>
+      </c>
+      <c r="N30">
+        <v>46512.20847222222</v>
       </c>
       <c r="O30" t="str">
         <v>Highnoon</v>
       </c>
       <c r="P30" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q30" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R30">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="31">
@@ -2088,9 +1913,9 @@
         <v>tablet</v>
       </c>
       <c r="C31" t="str">
-        <v>MED-030</v>
-      </c>
-      <c r="D31" t="str">
+        <v>SMP064345-030</v>
+      </c>
+      <c r="D31">
         <v>120</v>
       </c>
       <c r="E31" t="str">
@@ -2100,7 +1925,7 @@
         <v>Injectables</v>
       </c>
       <c r="G31" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H31">
         <v>78</v>
@@ -2111,29 +1936,23 @@
       <c r="J31">
         <v>68</v>
       </c>
-      <c r="K31" t="str">
-        <v>8901100000030</v>
+      <c r="K31">
+        <v>89064345030</v>
       </c>
       <c r="L31" t="str">
-        <v>BCH-2026-030</v>
-      </c>
-      <c r="M31" t="str">
-        <v>2026-06-03</v>
-      </c>
-      <c r="N31" t="str">
-        <v>2029-06-06</v>
+        <v>B064345-030</v>
+      </c>
+      <c r="M31">
+        <v>46176.20847222222</v>
+      </c>
+      <c r="N31">
+        <v>47275.20847222222</v>
       </c>
       <c r="O31" t="str">
         <v>Martin Dow</v>
       </c>
       <c r="P31" t="str">
         <v>No</v>
-      </c>
-      <c r="Q31" t="str">
-        <v/>
-      </c>
-      <c r="R31" t="str">
-        <v/>
       </c>
     </row>
     <row r="32">
@@ -2144,9 +1963,9 @@
         <v>tablet</v>
       </c>
       <c r="C32" t="str">
-        <v>MED-031</v>
-      </c>
-      <c r="D32" t="str">
+        <v>SMP064345-031</v>
+      </c>
+      <c r="D32">
         <v>5</v>
       </c>
       <c r="E32" t="str">
@@ -2156,7 +1975,7 @@
         <v>Analgesics</v>
       </c>
       <c r="G32" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H32">
         <v>81</v>
@@ -2167,29 +1986,23 @@
       <c r="J32">
         <v>70</v>
       </c>
-      <c r="K32" t="str">
-        <v>8901100000031</v>
+      <c r="K32">
+        <v>89064345031</v>
       </c>
       <c r="L32" t="str">
-        <v>BCH-2026-031</v>
-      </c>
-      <c r="M32" t="str">
-        <v>2025-07-04</v>
-      </c>
-      <c r="N32" t="str">
-        <v>2027-07-07</v>
+        <v>B064345-031</v>
+      </c>
+      <c r="M32">
+        <v>45842.20847222222</v>
+      </c>
+      <c r="N32">
+        <v>46575.20847222222</v>
       </c>
       <c r="O32" t="str">
         <v>Pfizer</v>
       </c>
       <c r="P32" t="str">
         <v>No</v>
-      </c>
-      <c r="Q32" t="str">
-        <v/>
-      </c>
-      <c r="R32" t="str">
-        <v/>
       </c>
     </row>
     <row r="33">
@@ -2200,9 +2013,9 @@
         <v>tablet</v>
       </c>
       <c r="C33" t="str">
-        <v>MED-032</v>
-      </c>
-      <c r="D33" t="str">
+        <v>SMP064345-032</v>
+      </c>
+      <c r="D33">
         <v>0.5</v>
       </c>
       <c r="E33" t="str">
@@ -2212,7 +2025,7 @@
         <v>Antibiotics</v>
       </c>
       <c r="G33" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H33">
         <v>84</v>
@@ -2223,29 +2036,23 @@
       <c r="J33">
         <v>72</v>
       </c>
-      <c r="K33" t="str">
-        <v>8901100000032</v>
+      <c r="K33">
+        <v>89064345032</v>
       </c>
       <c r="L33" t="str">
-        <v>BCH-2026-032</v>
-      </c>
-      <c r="M33" t="str">
-        <v>2026-08-05</v>
-      </c>
-      <c r="N33" t="str">
-        <v>2029-08-08</v>
+        <v>B064345-032</v>
+      </c>
+      <c r="M33">
+        <v>46239.20847222222</v>
+      </c>
+      <c r="N33">
+        <v>47338.20847222222</v>
       </c>
       <c r="O33" t="str">
         <v>Novartis</v>
       </c>
       <c r="P33" t="str">
         <v>No</v>
-      </c>
-      <c r="Q33" t="str">
-        <v/>
-      </c>
-      <c r="R33" t="str">
-        <v/>
       </c>
     </row>
     <row r="34">
@@ -2256,9 +2063,9 @@
         <v>tablet</v>
       </c>
       <c r="C34" t="str">
-        <v>MED-033</v>
-      </c>
-      <c r="D34" t="str">
+        <v>SMP064345-033</v>
+      </c>
+      <c r="D34">
         <v>75</v>
       </c>
       <c r="E34" t="str">
@@ -2268,7 +2075,7 @@
         <v>Antihistamines</v>
       </c>
       <c r="G34" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H34">
         <v>87</v>
@@ -2279,29 +2086,23 @@
       <c r="J34">
         <v>74</v>
       </c>
-      <c r="K34" t="str">
-        <v>8901100000033</v>
+      <c r="K34">
+        <v>89064345033</v>
       </c>
       <c r="L34" t="str">
-        <v>BCH-2026-033</v>
-      </c>
-      <c r="M34" t="str">
-        <v>2025-09-06</v>
-      </c>
-      <c r="N34" t="str">
-        <v>2027-09-09</v>
+        <v>B064345-033</v>
+      </c>
+      <c r="M34">
+        <v>45906.20847222222</v>
+      </c>
+      <c r="N34">
+        <v>46639.20847222222</v>
       </c>
       <c r="O34" t="str">
         <v>Generic</v>
       </c>
       <c r="P34" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q34" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R34">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="35">
@@ -2312,9 +2113,9 @@
         <v>tablet</v>
       </c>
       <c r="C35" t="str">
-        <v>MED-034</v>
-      </c>
-      <c r="D35" t="str">
+        <v>SMP064345-034</v>
+      </c>
+      <c r="D35">
         <v>75</v>
       </c>
       <c r="E35" t="str">
@@ -2324,7 +2125,7 @@
         <v>Antacids</v>
       </c>
       <c r="G35" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H35">
         <v>90</v>
@@ -2335,29 +2136,23 @@
       <c r="J35">
         <v>76</v>
       </c>
-      <c r="K35" t="str">
-        <v>8901100000034</v>
+      <c r="K35">
+        <v>89064345034</v>
       </c>
       <c r="L35" t="str">
-        <v>BCH-2026-034</v>
-      </c>
-      <c r="M35" t="str">
-        <v>2026-10-07</v>
-      </c>
-      <c r="N35" t="str">
-        <v>2029-10-10</v>
+        <v>B064345-034</v>
+      </c>
+      <c r="M35">
+        <v>46302.20847222222</v>
+      </c>
+      <c r="N35">
+        <v>47401.20847222222</v>
       </c>
       <c r="O35" t="str">
         <v>Getz</v>
       </c>
       <c r="P35" t="str">
         <v>No</v>
-      </c>
-      <c r="Q35" t="str">
-        <v/>
-      </c>
-      <c r="R35" t="str">
-        <v/>
       </c>
     </row>
     <row r="36">
@@ -2368,9 +2163,9 @@
         <v>tablet</v>
       </c>
       <c r="C36" t="str">
-        <v>MED-035</v>
-      </c>
-      <c r="D36" t="str">
+        <v>SMP064345-035</v>
+      </c>
+      <c r="D36">
         <v>5</v>
       </c>
       <c r="E36" t="str">
@@ -2380,7 +2175,7 @@
         <v>Cardiovascular</v>
       </c>
       <c r="G36" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H36">
         <v>93</v>
@@ -2391,29 +2186,23 @@
       <c r="J36">
         <v>78</v>
       </c>
-      <c r="K36" t="str">
-        <v>8901100000035</v>
+      <c r="K36">
+        <v>89064345035</v>
       </c>
       <c r="L36" t="str">
-        <v>BCH-2026-035</v>
-      </c>
-      <c r="M36" t="str">
-        <v>2025-11-08</v>
-      </c>
-      <c r="N36" t="str">
-        <v>2027-11-11</v>
+        <v>B064345-035</v>
+      </c>
+      <c r="M36">
+        <v>45969.20847222222</v>
+      </c>
+      <c r="N36">
+        <v>46702.20847222222</v>
       </c>
       <c r="O36" t="str">
         <v>Searle</v>
       </c>
       <c r="P36" t="str">
         <v>No</v>
-      </c>
-      <c r="Q36" t="str">
-        <v/>
-      </c>
-      <c r="R36" t="str">
-        <v/>
       </c>
     </row>
     <row r="37">
@@ -2424,9 +2213,9 @@
         <v>tablet</v>
       </c>
       <c r="C37" t="str">
-        <v>MED-036</v>
-      </c>
-      <c r="D37" t="str">
+        <v>SMP064345-036</v>
+      </c>
+      <c r="D37">
         <v>40</v>
       </c>
       <c r="E37" t="str">
@@ -2436,7 +2225,7 @@
         <v>Diabetes</v>
       </c>
       <c r="G37" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H37">
         <v>92.5</v>
@@ -2447,29 +2236,23 @@
       <c r="J37">
         <v>80</v>
       </c>
-      <c r="K37" t="str">
-        <v>8901100000036</v>
+      <c r="K37">
+        <v>89064345036</v>
       </c>
       <c r="L37" t="str">
-        <v>BCH-2026-036</v>
-      </c>
-      <c r="M37" t="str">
-        <v>2026-12-09</v>
-      </c>
-      <c r="N37" t="str">
-        <v>2029-12-12</v>
+        <v>B064345-036</v>
+      </c>
+      <c r="M37">
+        <v>46365.20847222222</v>
+      </c>
+      <c r="N37">
+        <v>47464.20847222222</v>
       </c>
       <c r="O37" t="str">
         <v>GSK</v>
       </c>
       <c r="P37" t="str">
         <v>No</v>
-      </c>
-      <c r="Q37" t="str">
-        <v/>
-      </c>
-      <c r="R37" t="str">
-        <v/>
       </c>
     </row>
     <row r="38">
@@ -2480,9 +2263,9 @@
         <v>tablet</v>
       </c>
       <c r="C38" t="str">
-        <v>MED-037</v>
-      </c>
-      <c r="D38" t="str">
+        <v>SMP064345-037</v>
+      </c>
+      <c r="D38">
         <v>25</v>
       </c>
       <c r="E38" t="str">
@@ -2492,7 +2275,7 @@
         <v>Vitamins</v>
       </c>
       <c r="G38" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H38">
         <v>95.5</v>
@@ -2503,29 +2286,23 @@
       <c r="J38">
         <v>82</v>
       </c>
-      <c r="K38" t="str">
-        <v>8901100000037</v>
+      <c r="K38">
+        <v>89064345037</v>
       </c>
       <c r="L38" t="str">
-        <v>BCH-2026-037</v>
-      </c>
-      <c r="M38" t="str">
-        <v>2025-01-10</v>
-      </c>
-      <c r="N38" t="str">
-        <v>2027-01-13</v>
+        <v>B064345-037</v>
+      </c>
+      <c r="M38">
+        <v>45667.20847222222</v>
+      </c>
+      <c r="N38">
+        <v>46400.20847222222</v>
       </c>
       <c r="O38" t="str">
         <v>Abbott</v>
       </c>
       <c r="P38" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q38" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R38">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="39">
@@ -2536,9 +2313,9 @@
         <v>tablet</v>
       </c>
       <c r="C39" t="str">
-        <v>MED-038</v>
-      </c>
-      <c r="D39" t="str">
+        <v>SMP064345-038</v>
+      </c>
+      <c r="D39">
         <v>5</v>
       </c>
       <c r="E39" t="str">
@@ -2548,7 +2325,7 @@
         <v>Respiratory</v>
       </c>
       <c r="G39" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H39">
         <v>98.5</v>
@@ -2559,29 +2336,23 @@
       <c r="J39">
         <v>84</v>
       </c>
-      <c r="K39" t="str">
-        <v>8901100000038</v>
+      <c r="K39">
+        <v>89064345038</v>
       </c>
       <c r="L39" t="str">
-        <v>BCH-2026-038</v>
-      </c>
-      <c r="M39" t="str">
-        <v>2026-02-11</v>
-      </c>
-      <c r="N39" t="str">
-        <v>2029-02-14</v>
+        <v>B064345-038</v>
+      </c>
+      <c r="M39">
+        <v>46064.20847222222</v>
+      </c>
+      <c r="N39">
+        <v>47163.20847222222</v>
       </c>
       <c r="O39" t="str">
         <v>Hilton</v>
       </c>
       <c r="P39" t="str">
         <v>No</v>
-      </c>
-      <c r="Q39" t="str">
-        <v/>
-      </c>
-      <c r="R39" t="str">
-        <v/>
       </c>
     </row>
     <row r="40">
@@ -2592,9 +2363,9 @@
         <v>tablet</v>
       </c>
       <c r="C40" t="str">
-        <v>MED-039</v>
-      </c>
-      <c r="D40" t="str">
+        <v>SMP064345-039</v>
+      </c>
+      <c r="D40">
         <v>80</v>
       </c>
       <c r="E40" t="str">
@@ -2604,7 +2375,7 @@
         <v>Dermatology</v>
       </c>
       <c r="G40" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H40">
         <v>101.5</v>
@@ -2615,29 +2386,23 @@
       <c r="J40">
         <v>86</v>
       </c>
-      <c r="K40" t="str">
-        <v>8901100000039</v>
+      <c r="K40">
+        <v>89064345039</v>
       </c>
       <c r="L40" t="str">
-        <v>BCH-2026-039</v>
-      </c>
-      <c r="M40" t="str">
-        <v>2025-03-12</v>
-      </c>
-      <c r="N40" t="str">
-        <v>2027-03-15</v>
+        <v>B064345-039</v>
+      </c>
+      <c r="M40">
+        <v>45728.20847222222</v>
+      </c>
+      <c r="N40">
+        <v>46461.20847222222</v>
       </c>
       <c r="O40" t="str">
         <v>Sami</v>
       </c>
       <c r="P40" t="str">
         <v>No</v>
-      </c>
-      <c r="Q40" t="str">
-        <v/>
-      </c>
-      <c r="R40" t="str">
-        <v/>
       </c>
     </row>
     <row r="41">
@@ -2648,9 +2413,9 @@
         <v>tablet</v>
       </c>
       <c r="C41" t="str">
-        <v>MED-040</v>
-      </c>
-      <c r="D41" t="str">
+        <v>SMP064345-040</v>
+      </c>
+      <c r="D41">
         <v>50</v>
       </c>
       <c r="E41" t="str">
@@ -2660,7 +2425,7 @@
         <v>Injectables</v>
       </c>
       <c r="G41" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H41">
         <v>104.5</v>
@@ -2671,29 +2436,23 @@
       <c r="J41">
         <v>88</v>
       </c>
-      <c r="K41" t="str">
-        <v>8901100000040</v>
+      <c r="K41">
+        <v>89064345040</v>
       </c>
       <c r="L41" t="str">
-        <v>BCH-2026-040</v>
-      </c>
-      <c r="M41" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="N41" t="str">
-        <v>2029-04-16</v>
+        <v>B064345-040</v>
+      </c>
+      <c r="M41">
+        <v>46125.20847222222</v>
+      </c>
+      <c r="N41">
+        <v>47224.20847222222</v>
       </c>
       <c r="O41" t="str">
         <v>Highnoon</v>
       </c>
       <c r="P41" t="str">
         <v>No</v>
-      </c>
-      <c r="Q41" t="str">
-        <v/>
-      </c>
-      <c r="R41" t="str">
-        <v/>
       </c>
     </row>
     <row r="42">
@@ -2704,9 +2463,9 @@
         <v>injection</v>
       </c>
       <c r="C42" t="str">
-        <v>MED-041</v>
-      </c>
-      <c r="D42" t="str">
+        <v>SMP064345-041</v>
+      </c>
+      <c r="D42">
         <v>100</v>
       </c>
       <c r="E42" t="str">
@@ -2716,7 +2475,7 @@
         <v>Analgesics</v>
       </c>
       <c r="G42" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H42">
         <v>7.5</v>
@@ -2727,29 +2486,23 @@
       <c r="J42">
         <v>90</v>
       </c>
-      <c r="K42" t="str">
-        <v>8901100000041</v>
+      <c r="K42">
+        <v>89064345041</v>
       </c>
       <c r="L42" t="str">
-        <v>BCH-2026-041</v>
-      </c>
-      <c r="M42" t="str">
-        <v>2025-05-14</v>
-      </c>
-      <c r="N42" t="str">
-        <v>2027-05-17</v>
+        <v>B064345-041</v>
+      </c>
+      <c r="M42">
+        <v>45791.20847222222</v>
+      </c>
+      <c r="N42">
+        <v>46524.20847222222</v>
       </c>
       <c r="O42" t="str">
         <v>Martin Dow</v>
       </c>
       <c r="P42" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q42" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R42">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="43">
@@ -2760,9 +2513,9 @@
         <v>injection</v>
       </c>
       <c r="C43" t="str">
-        <v>MED-042</v>
-      </c>
-      <c r="D43" t="str">
+        <v>SMP064345-042</v>
+      </c>
+      <c r="D43">
         <v>1</v>
       </c>
       <c r="E43" t="str">
@@ -2772,7 +2525,7 @@
         <v>Antibiotics</v>
       </c>
       <c r="G43" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H43">
         <v>10.5</v>
@@ -2783,29 +2536,23 @@
       <c r="J43">
         <v>92</v>
       </c>
-      <c r="K43" t="str">
-        <v>8901100000042</v>
+      <c r="K43">
+        <v>89064345042</v>
       </c>
       <c r="L43" t="str">
-        <v>BCH-2026-042</v>
-      </c>
-      <c r="M43" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="N43" t="str">
-        <v>2029-06-18</v>
+        <v>B064345-042</v>
+      </c>
+      <c r="M43">
+        <v>46188.20847222222</v>
+      </c>
+      <c r="N43">
+        <v>47287.20847222222</v>
       </c>
       <c r="O43" t="str">
         <v>Pfizer</v>
       </c>
       <c r="P43" t="str">
         <v>No</v>
-      </c>
-      <c r="Q43" t="str">
-        <v/>
-      </c>
-      <c r="R43" t="str">
-        <v/>
       </c>
     </row>
     <row r="44">
@@ -2816,9 +2563,9 @@
         <v>capsule</v>
       </c>
       <c r="C44" t="str">
-        <v>MED-043</v>
-      </c>
-      <c r="D44" t="str">
+        <v>SMP064345-043</v>
+      </c>
+      <c r="D44">
         <v>400</v>
       </c>
       <c r="E44" t="str">
@@ -2828,7 +2575,7 @@
         <v>Antihistamines</v>
       </c>
       <c r="G44" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H44">
         <v>10</v>
@@ -2839,29 +2586,23 @@
       <c r="J44">
         <v>94</v>
       </c>
-      <c r="K44" t="str">
-        <v>8901100000043</v>
+      <c r="K44">
+        <v>89064345043</v>
       </c>
       <c r="L44" t="str">
-        <v>BCH-2026-043</v>
-      </c>
-      <c r="M44" t="str">
-        <v>2025-07-16</v>
-      </c>
-      <c r="N44" t="str">
-        <v>2027-07-19</v>
+        <v>B064345-043</v>
+      </c>
+      <c r="M44">
+        <v>45854.20847222222</v>
+      </c>
+      <c r="N44">
+        <v>46587.20847222222</v>
       </c>
       <c r="O44" t="str">
         <v>Novartis</v>
       </c>
       <c r="P44" t="str">
         <v>No</v>
-      </c>
-      <c r="Q44" t="str">
-        <v/>
-      </c>
-      <c r="R44" t="str">
-        <v/>
       </c>
     </row>
     <row r="45">
@@ -2872,9 +2613,9 @@
         <v>tablet</v>
       </c>
       <c r="C45" t="str">
-        <v>MED-044</v>
-      </c>
-      <c r="D45" t="str">
+        <v>SMP064345-044</v>
+      </c>
+      <c r="D45">
         <v>600</v>
       </c>
       <c r="E45" t="str">
@@ -2884,7 +2625,7 @@
         <v>Antacids</v>
       </c>
       <c r="G45" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H45">
         <v>13</v>
@@ -2895,29 +2636,23 @@
       <c r="J45">
         <v>96</v>
       </c>
-      <c r="K45" t="str">
-        <v>8901100000044</v>
+      <c r="K45">
+        <v>89064345044</v>
       </c>
       <c r="L45" t="str">
-        <v>BCH-2026-044</v>
-      </c>
-      <c r="M45" t="str">
-        <v>2026-08-17</v>
-      </c>
-      <c r="N45" t="str">
-        <v>2029-08-20</v>
+        <v>B064345-044</v>
+      </c>
+      <c r="M45">
+        <v>46251.20847222222</v>
+      </c>
+      <c r="N45">
+        <v>47350.20847222222</v>
       </c>
       <c r="O45" t="str">
         <v>Generic</v>
       </c>
       <c r="P45" t="str">
         <v>No</v>
-      </c>
-      <c r="Q45" t="str">
-        <v/>
-      </c>
-      <c r="R45" t="str">
-        <v/>
       </c>
     </row>
     <row r="46">
@@ -2928,9 +2663,9 @@
         <v>tablet</v>
       </c>
       <c r="C46" t="str">
-        <v>MED-045</v>
-      </c>
-      <c r="D46" t="str">
+        <v>SMP064345-045</v>
+      </c>
+      <c r="D46">
         <v>400</v>
       </c>
       <c r="E46" t="str">
@@ -2940,7 +2675,7 @@
         <v>Cardiovascular</v>
       </c>
       <c r="G46" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H46">
         <v>16</v>
@@ -2951,29 +2686,23 @@
       <c r="J46">
         <v>98</v>
       </c>
-      <c r="K46" t="str">
-        <v>8901100000045</v>
+      <c r="K46">
+        <v>89064345045</v>
       </c>
       <c r="L46" t="str">
-        <v>BCH-2026-045</v>
-      </c>
-      <c r="M46" t="str">
-        <v>2025-09-18</v>
-      </c>
-      <c r="N46" t="str">
-        <v>2027-09-21</v>
+        <v>B064345-045</v>
+      </c>
+      <c r="M46">
+        <v>45918.20847222222</v>
+      </c>
+      <c r="N46">
+        <v>46651.20847222222</v>
       </c>
       <c r="O46" t="str">
         <v>Getz</v>
       </c>
       <c r="P46" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q46" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R46">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="47">
@@ -2984,9 +2713,9 @@
         <v>tablet</v>
       </c>
       <c r="C47" t="str">
-        <v>MED-046</v>
-      </c>
-      <c r="D47" t="str">
+        <v>SMP064345-046</v>
+      </c>
+      <c r="D47">
         <v>500</v>
       </c>
       <c r="E47" t="str">
@@ -2996,7 +2725,7 @@
         <v>Diabetes</v>
       </c>
       <c r="G47" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H47">
         <v>19</v>
@@ -3007,29 +2736,23 @@
       <c r="J47">
         <v>100</v>
       </c>
-      <c r="K47" t="str">
-        <v>8901100000046</v>
+      <c r="K47">
+        <v>89064345046</v>
       </c>
       <c r="L47" t="str">
-        <v>BCH-2026-046</v>
-      </c>
-      <c r="M47" t="str">
-        <v>2026-10-19</v>
-      </c>
-      <c r="N47" t="str">
-        <v>2029-10-22</v>
+        <v>B064345-046</v>
+      </c>
+      <c r="M47">
+        <v>46314.20847222222</v>
+      </c>
+      <c r="N47">
+        <v>47413.20847222222</v>
       </c>
       <c r="O47" t="str">
         <v>Searle</v>
       </c>
       <c r="P47" t="str">
         <v>No</v>
-      </c>
-      <c r="Q47" t="str">
-        <v/>
-      </c>
-      <c r="R47" t="str">
-        <v/>
       </c>
     </row>
     <row r="48">
@@ -3040,9 +2763,9 @@
         <v>capsule</v>
       </c>
       <c r="C48" t="str">
-        <v>MED-047</v>
-      </c>
-      <c r="D48" t="str">
+        <v>SMP064345-047</v>
+      </c>
+      <c r="D48">
         <v>50000</v>
       </c>
       <c r="E48" t="str">
@@ -3052,7 +2775,7 @@
         <v>Vitamins</v>
       </c>
       <c r="G48" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H48">
         <v>22</v>
@@ -3063,29 +2786,23 @@
       <c r="J48">
         <v>102</v>
       </c>
-      <c r="K48" t="str">
-        <v>8901100000047</v>
+      <c r="K48">
+        <v>89064345047</v>
       </c>
       <c r="L48" t="str">
-        <v>BCH-2026-047</v>
-      </c>
-      <c r="M48" t="str">
-        <v>2025-11-20</v>
-      </c>
-      <c r="N48" t="str">
-        <v>2027-11-23</v>
+        <v>B064345-047</v>
+      </c>
+      <c r="M48">
+        <v>45981.20847222222</v>
+      </c>
+      <c r="N48">
+        <v>46714.20847222222</v>
       </c>
       <c r="O48" t="str">
         <v>GSK</v>
       </c>
       <c r="P48" t="str">
         <v>No</v>
-      </c>
-      <c r="Q48" t="str">
-        <v/>
-      </c>
-      <c r="R48" t="str">
-        <v/>
       </c>
     </row>
     <row r="49">
@@ -3096,9 +2813,9 @@
         <v>injection</v>
       </c>
       <c r="C49" t="str">
-        <v>MED-048</v>
-      </c>
-      <c r="D49" t="str">
+        <v>SMP064345-048</v>
+      </c>
+      <c r="D49">
         <v>1000</v>
       </c>
       <c r="E49" t="str">
@@ -3108,7 +2825,7 @@
         <v>Respiratory</v>
       </c>
       <c r="G49" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H49">
         <v>25</v>
@@ -3119,29 +2836,23 @@
       <c r="J49">
         <v>104</v>
       </c>
-      <c r="K49" t="str">
-        <v>8901100000048</v>
+      <c r="K49">
+        <v>89064345048</v>
       </c>
       <c r="L49" t="str">
-        <v>BCH-2026-048</v>
-      </c>
-      <c r="M49" t="str">
-        <v>2026-12-21</v>
-      </c>
-      <c r="N49" t="str">
-        <v>2029-12-24</v>
+        <v>B064345-048</v>
+      </c>
+      <c r="M49">
+        <v>46377.20847222222</v>
+      </c>
+      <c r="N49">
+        <v>47476.20847222222</v>
       </c>
       <c r="O49" t="str">
         <v>Abbott</v>
       </c>
       <c r="P49" t="str">
         <v>No</v>
-      </c>
-      <c r="Q49" t="str">
-        <v/>
-      </c>
-      <c r="R49" t="str">
-        <v/>
       </c>
     </row>
     <row r="50">
@@ -3152,9 +2863,9 @@
         <v>tablet</v>
       </c>
       <c r="C50" t="str">
-        <v>MED-049</v>
-      </c>
-      <c r="D50" t="str">
+        <v>SMP064345-049</v>
+      </c>
+      <c r="D50">
         <v>5</v>
       </c>
       <c r="E50" t="str">
@@ -3164,7 +2875,7 @@
         <v>Dermatology</v>
       </c>
       <c r="G50" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H50">
         <v>28</v>
@@ -3175,29 +2886,23 @@
       <c r="J50">
         <v>106</v>
       </c>
-      <c r="K50" t="str">
-        <v>8901100000049</v>
+      <c r="K50">
+        <v>89064345049</v>
       </c>
       <c r="L50" t="str">
-        <v>BCH-2026-049</v>
-      </c>
-      <c r="M50" t="str">
-        <v>2025-01-22</v>
-      </c>
-      <c r="N50" t="str">
-        <v>2027-01-25</v>
+        <v>B064345-049</v>
+      </c>
+      <c r="M50">
+        <v>45679.20847222222</v>
+      </c>
+      <c r="N50">
+        <v>46412.20847222222</v>
       </c>
       <c r="O50" t="str">
         <v>Hilton</v>
       </c>
       <c r="P50" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q50" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R50">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="51">
@@ -3208,9 +2913,9 @@
         <v>syrup</v>
       </c>
       <c r="C51" t="str">
-        <v>MED-050</v>
-      </c>
-      <c r="D51" t="str">
+        <v>SMP064345-050</v>
+      </c>
+      <c r="D51">
         <v>50</v>
       </c>
       <c r="E51" t="str">
@@ -3220,7 +2925,7 @@
         <v>Injectables</v>
       </c>
       <c r="G51" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H51">
         <v>27.5</v>
@@ -3231,29 +2936,23 @@
       <c r="J51">
         <v>108</v>
       </c>
-      <c r="K51" t="str">
-        <v>8901100000050</v>
+      <c r="K51">
+        <v>89064345050</v>
       </c>
       <c r="L51" t="str">
-        <v>BCH-2026-050</v>
-      </c>
-      <c r="M51" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="N51" t="str">
-        <v>2029-02-26</v>
+        <v>B064345-050</v>
+      </c>
+      <c r="M51">
+        <v>46076.20847222222</v>
+      </c>
+      <c r="N51">
+        <v>47175.20847222222</v>
       </c>
       <c r="O51" t="str">
         <v>Sami</v>
       </c>
       <c r="P51" t="str">
         <v>No</v>
-      </c>
-      <c r="Q51" t="str">
-        <v/>
-      </c>
-      <c r="R51" t="str">
-        <v/>
       </c>
     </row>
     <row r="52">
@@ -3264,9 +2963,9 @@
         <v>pcs</v>
       </c>
       <c r="C52" t="str">
-        <v>MED-051</v>
-      </c>
-      <c r="D52" t="str">
+        <v>SMP064345-051</v>
+      </c>
+      <c r="D52">
         <v>20.5</v>
       </c>
       <c r="E52" t="str">
@@ -3276,7 +2975,7 @@
         <v>Analgesics</v>
       </c>
       <c r="G52" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H52">
         <v>30.5</v>
@@ -3287,29 +2986,23 @@
       <c r="J52">
         <v>10</v>
       </c>
-      <c r="K52" t="str">
-        <v>8901100000051</v>
+      <c r="K52">
+        <v>89064345051</v>
       </c>
       <c r="L52" t="str">
-        <v>BCH-2026-051</v>
-      </c>
-      <c r="M52" t="str">
-        <v>2025-03-24</v>
-      </c>
-      <c r="N52" t="str">
-        <v>2027-03-27</v>
+        <v>B064345-051</v>
+      </c>
+      <c r="M52">
+        <v>45740.20847222222</v>
+      </c>
+      <c r="N52">
+        <v>46473.20847222222</v>
       </c>
       <c r="O52" t="str">
         <v>Highnoon</v>
       </c>
       <c r="P52" t="str">
         <v>No</v>
-      </c>
-      <c r="Q52" t="str">
-        <v/>
-      </c>
-      <c r="R52" t="str">
-        <v/>
       </c>
     </row>
     <row r="53">
@@ -3320,9 +3013,9 @@
         <v>tablet</v>
       </c>
       <c r="C53" t="str">
-        <v>MED-052</v>
-      </c>
-      <c r="D53" t="str">
+        <v>SMP064345-052</v>
+      </c>
+      <c r="D53">
         <v>500</v>
       </c>
       <c r="E53" t="str">
@@ -3332,7 +3025,7 @@
         <v>Antibiotics</v>
       </c>
       <c r="G53" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H53">
         <v>33.5</v>
@@ -3343,29 +3036,23 @@
       <c r="J53">
         <v>12</v>
       </c>
-      <c r="K53" t="str">
-        <v>8901100000052</v>
+      <c r="K53">
+        <v>89064345052</v>
       </c>
       <c r="L53" t="str">
-        <v>BCH-2026-052</v>
-      </c>
-      <c r="M53" t="str">
-        <v>2026-04-25</v>
-      </c>
-      <c r="N53" t="str">
-        <v>2029-04-28</v>
+        <v>B064345-052</v>
+      </c>
+      <c r="M53">
+        <v>46137.20847222222</v>
+      </c>
+      <c r="N53">
+        <v>47236.20847222222</v>
       </c>
       <c r="O53" t="str">
         <v>Martin Dow</v>
       </c>
       <c r="P53" t="str">
         <v>No</v>
-      </c>
-      <c r="Q53" t="str">
-        <v/>
-      </c>
-      <c r="R53" t="str">
-        <v/>
       </c>
     </row>
     <row r="54">
@@ -3376,9 +3063,9 @@
         <v>syrup</v>
       </c>
       <c r="C54" t="str">
-        <v>MED-053</v>
-      </c>
-      <c r="D54" t="str">
+        <v>SMP064345-053</v>
+      </c>
+      <c r="D54">
         <v>5</v>
       </c>
       <c r="E54" t="str">
@@ -3388,7 +3075,7 @@
         <v>Antihistamines</v>
       </c>
       <c r="G54" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H54">
         <v>36.5</v>
@@ -3399,29 +3086,23 @@
       <c r="J54">
         <v>14</v>
       </c>
-      <c r="K54" t="str">
-        <v>8901100000053</v>
+      <c r="K54">
+        <v>89064345053</v>
       </c>
       <c r="L54" t="str">
-        <v>BCH-2026-053</v>
-      </c>
-      <c r="M54" t="str">
-        <v>2025-05-26</v>
-      </c>
-      <c r="N54" t="str">
-        <v>2027-05-28</v>
+        <v>B064345-053</v>
+      </c>
+      <c r="M54">
+        <v>45803.20847222222</v>
+      </c>
+      <c r="N54">
+        <v>46535.20847222222</v>
       </c>
       <c r="O54" t="str">
         <v>Pfizer</v>
       </c>
       <c r="P54" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q54" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R54">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="55">
@@ -3432,9 +3113,9 @@
         <v>syrup</v>
       </c>
       <c r="C55" t="str">
-        <v>MED-054</v>
-      </c>
-      <c r="D55" t="str">
+        <v>SMP064345-054</v>
+      </c>
+      <c r="D55">
         <v>2</v>
       </c>
       <c r="E55" t="str">
@@ -3444,7 +3125,7 @@
         <v>Antacids</v>
       </c>
       <c r="G55" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H55">
         <v>39.5</v>
@@ -3455,29 +3136,23 @@
       <c r="J55">
         <v>16</v>
       </c>
-      <c r="K55" t="str">
-        <v>8901100000054</v>
+      <c r="K55">
+        <v>89064345054</v>
       </c>
       <c r="L55" t="str">
-        <v>BCH-2026-054</v>
-      </c>
-      <c r="M55" t="str">
-        <v>2026-06-27</v>
-      </c>
-      <c r="N55" t="str">
-        <v>2029-06-28</v>
+        <v>B064345-054</v>
+      </c>
+      <c r="M55">
+        <v>46200.20847222222</v>
+      </c>
+      <c r="N55">
+        <v>47297.20847222222</v>
       </c>
       <c r="O55" t="str">
         <v>Novartis</v>
       </c>
       <c r="P55" t="str">
         <v>No</v>
-      </c>
-      <c r="Q55" t="str">
-        <v/>
-      </c>
-      <c r="R55" t="str">
-        <v/>
       </c>
     </row>
     <row r="56">
@@ -3488,9 +3163,9 @@
         <v>syrup</v>
       </c>
       <c r="C56" t="str">
-        <v>MED-055</v>
-      </c>
-      <c r="D56" t="str">
+        <v>SMP064345-055</v>
+      </c>
+      <c r="D56">
         <v>15</v>
       </c>
       <c r="E56" t="str">
@@ -3500,7 +3175,7 @@
         <v>Cardiovascular</v>
       </c>
       <c r="G56" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H56">
         <v>42.5</v>
@@ -3511,29 +3186,23 @@
       <c r="J56">
         <v>18</v>
       </c>
-      <c r="K56" t="str">
-        <v>8901100000055</v>
+      <c r="K56">
+        <v>89064345055</v>
       </c>
       <c r="L56" t="str">
-        <v>BCH-2026-055</v>
-      </c>
-      <c r="M56" t="str">
-        <v>2025-07-01</v>
-      </c>
-      <c r="N56" t="str">
-        <v>2027-07-04</v>
+        <v>B064345-055</v>
+      </c>
+      <c r="M56">
+        <v>45839.20847222222</v>
+      </c>
+      <c r="N56">
+        <v>46572.20847222222</v>
       </c>
       <c r="O56" t="str">
         <v>Generic</v>
       </c>
       <c r="P56" t="str">
         <v>No</v>
-      </c>
-      <c r="Q56" t="str">
-        <v/>
-      </c>
-      <c r="R56" t="str">
-        <v/>
       </c>
     </row>
     <row r="57">
@@ -3544,9 +3213,9 @@
         <v>syrup</v>
       </c>
       <c r="C57" t="str">
-        <v>MED-056</v>
-      </c>
-      <c r="D57" t="str">
+        <v>SMP064345-056</v>
+      </c>
+      <c r="D57">
         <v>30</v>
       </c>
       <c r="E57" t="str">
@@ -3556,7 +3225,7 @@
         <v>Diabetes</v>
       </c>
       <c r="G57" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H57">
         <v>45.5</v>
@@ -3567,29 +3236,23 @@
       <c r="J57">
         <v>20</v>
       </c>
-      <c r="K57" t="str">
-        <v>8901100000056</v>
+      <c r="K57">
+        <v>89064345056</v>
       </c>
       <c r="L57" t="str">
-        <v>BCH-2026-056</v>
-      </c>
-      <c r="M57" t="str">
-        <v>2026-08-02</v>
-      </c>
-      <c r="N57" t="str">
-        <v>2029-08-05</v>
+        <v>B064345-056</v>
+      </c>
+      <c r="M57">
+        <v>46236.20847222222</v>
+      </c>
+      <c r="N57">
+        <v>47335.20847222222</v>
       </c>
       <c r="O57" t="str">
         <v>Getz</v>
       </c>
       <c r="P57" t="str">
         <v>No</v>
-      </c>
-      <c r="Q57" t="str">
-        <v/>
-      </c>
-      <c r="R57" t="str">
-        <v/>
       </c>
     </row>
     <row r="58">
@@ -3600,9 +3263,9 @@
         <v>cream</v>
       </c>
       <c r="C58" t="str">
-        <v>MED-057</v>
-      </c>
-      <c r="D58" t="str">
+        <v>SMP064345-057</v>
+      </c>
+      <c r="D58">
         <v>2</v>
       </c>
       <c r="E58" t="str">
@@ -3612,7 +3275,7 @@
         <v>Vitamins</v>
       </c>
       <c r="G58" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H58">
         <v>45</v>
@@ -3623,29 +3286,23 @@
       <c r="J58">
         <v>22</v>
       </c>
-      <c r="K58" t="str">
-        <v>8901100000057</v>
+      <c r="K58">
+        <v>89064345057</v>
       </c>
       <c r="L58" t="str">
-        <v>BCH-2026-057</v>
-      </c>
-      <c r="M58" t="str">
-        <v>2025-09-03</v>
-      </c>
-      <c r="N58" t="str">
-        <v>2027-09-06</v>
+        <v>B064345-057</v>
+      </c>
+      <c r="M58">
+        <v>45903.20847222222</v>
+      </c>
+      <c r="N58">
+        <v>46636.20847222222</v>
       </c>
       <c r="O58" t="str">
         <v>Searle</v>
       </c>
       <c r="P58" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q58" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R58">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="59">
@@ -3656,9 +3313,9 @@
         <v>cream</v>
       </c>
       <c r="C59" t="str">
-        <v>MED-058</v>
-      </c>
-      <c r="D59" t="str">
+        <v>SMP064345-058</v>
+      </c>
+      <c r="D59">
         <v>1</v>
       </c>
       <c r="E59" t="str">
@@ -3668,7 +3325,7 @@
         <v>Respiratory</v>
       </c>
       <c r="G59" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H59">
         <v>48</v>
@@ -3679,29 +3336,23 @@
       <c r="J59">
         <v>24</v>
       </c>
-      <c r="K59" t="str">
-        <v>8901100000058</v>
+      <c r="K59">
+        <v>89064345058</v>
       </c>
       <c r="L59" t="str">
-        <v>BCH-2026-058</v>
-      </c>
-      <c r="M59" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="N59" t="str">
-        <v>2029-10-07</v>
+        <v>B064345-058</v>
+      </c>
+      <c r="M59">
+        <v>46299.20847222222</v>
+      </c>
+      <c r="N59">
+        <v>47398.20847222222</v>
       </c>
       <c r="O59" t="str">
         <v>GSK</v>
       </c>
       <c r="P59" t="str">
         <v>No</v>
-      </c>
-      <c r="Q59" t="str">
-        <v/>
-      </c>
-      <c r="R59" t="str">
-        <v/>
       </c>
     </row>
     <row r="60">
@@ -3712,9 +3363,9 @@
         <v>ointment</v>
       </c>
       <c r="C60" t="str">
-        <v>MED-059</v>
-      </c>
-      <c r="D60" t="str">
+        <v>SMP064345-059</v>
+      </c>
+      <c r="D60">
         <v>1</v>
       </c>
       <c r="E60" t="str">
@@ -3724,7 +3375,7 @@
         <v>Dermatology</v>
       </c>
       <c r="G60" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H60">
         <v>51</v>
@@ -3735,29 +3386,23 @@
       <c r="J60">
         <v>26</v>
       </c>
-      <c r="K60" t="str">
-        <v>8901100000059</v>
+      <c r="K60">
+        <v>89064345059</v>
       </c>
       <c r="L60" t="str">
-        <v>BCH-2026-059</v>
-      </c>
-      <c r="M60" t="str">
-        <v>2025-11-05</v>
-      </c>
-      <c r="N60" t="str">
-        <v>2027-11-08</v>
+        <v>B064345-059</v>
+      </c>
+      <c r="M60">
+        <v>45966.20847222222</v>
+      </c>
+      <c r="N60">
+        <v>46699.20847222222</v>
       </c>
       <c r="O60" t="str">
         <v>Abbott</v>
       </c>
       <c r="P60" t="str">
         <v>No</v>
-      </c>
-      <c r="Q60" t="str">
-        <v/>
-      </c>
-      <c r="R60" t="str">
-        <v/>
       </c>
     </row>
     <row r="61">
@@ -3768,9 +3413,9 @@
         <v>cream</v>
       </c>
       <c r="C61" t="str">
-        <v>MED-060</v>
-      </c>
-      <c r="D61" t="str">
+        <v>SMP064345-060</v>
+      </c>
+      <c r="D61">
         <v>0.1</v>
       </c>
       <c r="E61" t="str">
@@ -3780,7 +3425,7 @@
         <v>Injectables</v>
       </c>
       <c r="G61" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H61">
         <v>54</v>
@@ -3791,29 +3436,23 @@
       <c r="J61">
         <v>28</v>
       </c>
-      <c r="K61" t="str">
-        <v>8901100000060</v>
+      <c r="K61">
+        <v>89064345060</v>
       </c>
       <c r="L61" t="str">
-        <v>BCH-2026-060</v>
-      </c>
-      <c r="M61" t="str">
-        <v>2026-12-06</v>
-      </c>
-      <c r="N61" t="str">
-        <v>2029-12-09</v>
+        <v>B064345-060</v>
+      </c>
+      <c r="M61">
+        <v>46362.20847222222</v>
+      </c>
+      <c r="N61">
+        <v>47461.20847222222</v>
       </c>
       <c r="O61" t="str">
         <v>Hilton</v>
       </c>
       <c r="P61" t="str">
         <v>No</v>
-      </c>
-      <c r="Q61" t="str">
-        <v/>
-      </c>
-      <c r="R61" t="str">
-        <v/>
       </c>
     </row>
     <row r="62">
@@ -3824,9 +3463,9 @@
         <v>cream</v>
       </c>
       <c r="C62" t="str">
-        <v>MED-061</v>
-      </c>
-      <c r="D62" t="str">
+        <v>SMP064345-061</v>
+      </c>
+      <c r="D62">
         <v>2</v>
       </c>
       <c r="E62" t="str">
@@ -3836,7 +3475,7 @@
         <v>Analgesics</v>
       </c>
       <c r="G62" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H62">
         <v>57</v>
@@ -3847,29 +3486,23 @@
       <c r="J62">
         <v>30</v>
       </c>
-      <c r="K62" t="str">
-        <v>8901100000061</v>
+      <c r="K62">
+        <v>89064345061</v>
       </c>
       <c r="L62" t="str">
-        <v>BCH-2026-061</v>
-      </c>
-      <c r="M62" t="str">
-        <v>2025-01-07</v>
-      </c>
-      <c r="N62" t="str">
-        <v>2027-01-10</v>
+        <v>B064345-061</v>
+      </c>
+      <c r="M62">
+        <v>45664.20847222222</v>
+      </c>
+      <c r="N62">
+        <v>46397.20847222222</v>
       </c>
       <c r="O62" t="str">
         <v>Sami</v>
       </c>
       <c r="P62" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q62" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R62">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="63">
@@ -3880,9 +3513,9 @@
         <v>ointment</v>
       </c>
       <c r="C63" t="str">
-        <v>MED-062</v>
-      </c>
-      <c r="D63" t="str">
+        <v>SMP064345-062</v>
+      </c>
+      <c r="D63">
         <v>2</v>
       </c>
       <c r="E63" t="str">
@@ -3892,7 +3525,7 @@
         <v>Antibiotics</v>
       </c>
       <c r="G63" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H63">
         <v>60</v>
@@ -3903,29 +3536,23 @@
       <c r="J63">
         <v>32</v>
       </c>
-      <c r="K63" t="str">
-        <v>8901100000062</v>
+      <c r="K63">
+        <v>89064345062</v>
       </c>
       <c r="L63" t="str">
-        <v>BCH-2026-062</v>
-      </c>
-      <c r="M63" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="N63" t="str">
-        <v>2029-02-11</v>
+        <v>B064345-062</v>
+      </c>
+      <c r="M63">
+        <v>46061.20847222222</v>
+      </c>
+      <c r="N63">
+        <v>47160.20847222222</v>
       </c>
       <c r="O63" t="str">
         <v>Highnoon</v>
       </c>
       <c r="P63" t="str">
         <v>No</v>
-      </c>
-      <c r="Q63" t="str">
-        <v/>
-      </c>
-      <c r="R63" t="str">
-        <v/>
       </c>
     </row>
     <row r="64">
@@ -3936,9 +3563,9 @@
         <v>drops</v>
       </c>
       <c r="C64" t="str">
-        <v>MED-063</v>
-      </c>
-      <c r="D64" t="str">
+        <v>SMP064345-063</v>
+      </c>
+      <c r="D64">
         <v>0.3</v>
       </c>
       <c r="E64" t="str">
@@ -3948,7 +3575,7 @@
         <v>Antihistamines</v>
       </c>
       <c r="G64" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H64">
         <v>63</v>
@@ -3959,29 +3586,23 @@
       <c r="J64">
         <v>34</v>
       </c>
-      <c r="K64" t="str">
-        <v>8901100000063</v>
+      <c r="K64">
+        <v>89064345063</v>
       </c>
       <c r="L64" t="str">
-        <v>BCH-2026-063</v>
-      </c>
-      <c r="M64" t="str">
-        <v>2025-03-09</v>
-      </c>
-      <c r="N64" t="str">
-        <v>2027-03-12</v>
+        <v>B064345-063</v>
+      </c>
+      <c r="M64">
+        <v>45725.20847222222</v>
+      </c>
+      <c r="N64">
+        <v>46458.20847222222</v>
       </c>
       <c r="O64" t="str">
         <v>Martin Dow</v>
       </c>
       <c r="P64" t="str">
         <v>No</v>
-      </c>
-      <c r="Q64" t="str">
-        <v/>
-      </c>
-      <c r="R64" t="str">
-        <v/>
       </c>
     </row>
     <row r="65">
@@ -3992,9 +3613,9 @@
         <v>drops</v>
       </c>
       <c r="C65" t="str">
-        <v>MED-064</v>
-      </c>
-      <c r="D65" t="str">
+        <v>SMP064345-064</v>
+      </c>
+      <c r="D65">
         <v>0.3</v>
       </c>
       <c r="E65" t="str">
@@ -4004,7 +3625,7 @@
         <v>Antacids</v>
       </c>
       <c r="G65" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H65">
         <v>62.5</v>
@@ -4015,29 +3636,23 @@
       <c r="J65">
         <v>36</v>
       </c>
-      <c r="K65" t="str">
-        <v>8901100000064</v>
+      <c r="K65">
+        <v>89064345064</v>
       </c>
       <c r="L65" t="str">
-        <v>BCH-2026-064</v>
-      </c>
-      <c r="M65" t="str">
-        <v>2026-04-10</v>
-      </c>
-      <c r="N65" t="str">
-        <v>2029-04-13</v>
+        <v>B064345-064</v>
+      </c>
+      <c r="M65">
+        <v>46122.20847222222</v>
+      </c>
+      <c r="N65">
+        <v>47221.20847222222</v>
       </c>
       <c r="O65" t="str">
         <v>Pfizer</v>
       </c>
       <c r="P65" t="str">
         <v>No</v>
-      </c>
-      <c r="Q65" t="str">
-        <v/>
-      </c>
-      <c r="R65" t="str">
-        <v/>
       </c>
     </row>
     <row r="66">
@@ -4048,9 +3663,9 @@
         <v>drops</v>
       </c>
       <c r="C66" t="str">
-        <v>MED-065</v>
-      </c>
-      <c r="D66" t="str">
+        <v>SMP064345-065</v>
+      </c>
+      <c r="D66">
         <v>0.5</v>
       </c>
       <c r="E66" t="str">
@@ -4060,7 +3675,7 @@
         <v>Cardiovascular</v>
       </c>
       <c r="G66" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H66">
         <v>65.5</v>
@@ -4071,29 +3686,23 @@
       <c r="J66">
         <v>38</v>
       </c>
-      <c r="K66" t="str">
-        <v>8901100000065</v>
+      <c r="K66">
+        <v>89064345065</v>
       </c>
       <c r="L66" t="str">
-        <v>BCH-2026-065</v>
-      </c>
-      <c r="M66" t="str">
-        <v>2025-05-11</v>
-      </c>
-      <c r="N66" t="str">
-        <v>2027-05-14</v>
+        <v>B064345-065</v>
+      </c>
+      <c r="M66">
+        <v>45788.20847222222</v>
+      </c>
+      <c r="N66">
+        <v>46521.20847222222</v>
       </c>
       <c r="O66" t="str">
         <v>Novartis</v>
       </c>
       <c r="P66" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q66" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R66">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="67">
@@ -4104,9 +3713,9 @@
         <v>drops</v>
       </c>
       <c r="C67" t="str">
-        <v>MED-066</v>
-      </c>
-      <c r="D67" t="str">
+        <v>SMP064345-066</v>
+      </c>
+      <c r="D67">
         <v>0.1</v>
       </c>
       <c r="E67" t="str">
@@ -4116,7 +3725,7 @@
         <v>Diabetes</v>
       </c>
       <c r="G67" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H67">
         <v>68.5</v>
@@ -4127,29 +3736,23 @@
       <c r="J67">
         <v>40</v>
       </c>
-      <c r="K67" t="str">
-        <v>8901100000066</v>
+      <c r="K67">
+        <v>89064345066</v>
       </c>
       <c r="L67" t="str">
-        <v>BCH-2026-066</v>
-      </c>
-      <c r="M67" t="str">
-        <v>2026-06-12</v>
-      </c>
-      <c r="N67" t="str">
-        <v>2029-06-15</v>
+        <v>B064345-066</v>
+      </c>
+      <c r="M67">
+        <v>46185.20847222222</v>
+      </c>
+      <c r="N67">
+        <v>47284.20847222222</v>
       </c>
       <c r="O67" t="str">
         <v>Generic</v>
       </c>
       <c r="P67" t="str">
         <v>No</v>
-      </c>
-      <c r="Q67" t="str">
-        <v/>
-      </c>
-      <c r="R67" t="str">
-        <v/>
       </c>
     </row>
     <row r="68">
@@ -4160,9 +3763,9 @@
         <v>injection</v>
       </c>
       <c r="C68" t="str">
-        <v>MED-067</v>
-      </c>
-      <c r="D68" t="str">
+        <v>SMP064345-067</v>
+      </c>
+      <c r="D68">
         <v>0.9</v>
       </c>
       <c r="E68" t="str">
@@ -4172,7 +3775,7 @@
         <v>Vitamins</v>
       </c>
       <c r="G68" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H68">
         <v>71.5</v>
@@ -4183,29 +3786,23 @@
       <c r="J68">
         <v>42</v>
       </c>
-      <c r="K68" t="str">
-        <v>8901100000067</v>
+      <c r="K68">
+        <v>89064345067</v>
       </c>
       <c r="L68" t="str">
-        <v>BCH-2026-067</v>
-      </c>
-      <c r="M68" t="str">
-        <v>2025-07-13</v>
-      </c>
-      <c r="N68" t="str">
-        <v>2027-07-16</v>
+        <v>B064345-067</v>
+      </c>
+      <c r="M68">
+        <v>45851.20847222222</v>
+      </c>
+      <c r="N68">
+        <v>46584.20847222222</v>
       </c>
       <c r="O68" t="str">
         <v>Getz</v>
       </c>
       <c r="P68" t="str">
         <v>No</v>
-      </c>
-      <c r="Q68" t="str">
-        <v/>
-      </c>
-      <c r="R68" t="str">
-        <v/>
       </c>
     </row>
     <row r="69">
@@ -4216,9 +3813,9 @@
         <v>injection</v>
       </c>
       <c r="C69" t="str">
-        <v>MED-068</v>
-      </c>
-      <c r="D69" t="str">
+        <v>SMP064345-068</v>
+      </c>
+      <c r="D69">
         <v>5</v>
       </c>
       <c r="E69" t="str">
@@ -4228,7 +3825,7 @@
         <v>Respiratory</v>
       </c>
       <c r="G69" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H69">
         <v>74.5</v>
@@ -4239,29 +3836,23 @@
       <c r="J69">
         <v>44</v>
       </c>
-      <c r="K69" t="str">
-        <v>8901100000068</v>
+      <c r="K69">
+        <v>89064345068</v>
       </c>
       <c r="L69" t="str">
-        <v>BCH-2026-068</v>
-      </c>
-      <c r="M69" t="str">
-        <v>2026-08-14</v>
-      </c>
-      <c r="N69" t="str">
-        <v>2029-08-17</v>
+        <v>B064345-068</v>
+      </c>
+      <c r="M69">
+        <v>46248.20847222222</v>
+      </c>
+      <c r="N69">
+        <v>47347.20847222222</v>
       </c>
       <c r="O69" t="str">
         <v>Searle</v>
       </c>
       <c r="P69" t="str">
         <v>No</v>
-      </c>
-      <c r="Q69" t="str">
-        <v/>
-      </c>
-      <c r="R69" t="str">
-        <v/>
       </c>
     </row>
     <row r="70">
@@ -4272,9 +3863,9 @@
         <v>capsule</v>
       </c>
       <c r="C70" t="str">
-        <v>MED-069</v>
-      </c>
-      <c r="D70" t="str">
+        <v>SMP064345-069</v>
+      </c>
+      <c r="D70">
         <v>50</v>
       </c>
       <c r="E70" t="str">
@@ -4284,7 +3875,7 @@
         <v>Dermatology</v>
       </c>
       <c r="G70" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H70">
         <v>77.5</v>
@@ -4295,29 +3886,23 @@
       <c r="J70">
         <v>46</v>
       </c>
-      <c r="K70" t="str">
-        <v>8901100000069</v>
+      <c r="K70">
+        <v>89064345069</v>
       </c>
       <c r="L70" t="str">
-        <v>BCH-2026-069</v>
-      </c>
-      <c r="M70" t="str">
-        <v>2025-09-15</v>
-      </c>
-      <c r="N70" t="str">
-        <v>2027-09-18</v>
+        <v>B064345-069</v>
+      </c>
+      <c r="M70">
+        <v>45915.20847222222</v>
+      </c>
+      <c r="N70">
+        <v>46648.20847222222</v>
       </c>
       <c r="O70" t="str">
         <v>GSK</v>
       </c>
       <c r="P70" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q70" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R70">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="71">
@@ -4328,9 +3913,9 @@
         <v>tablet</v>
       </c>
       <c r="C71" t="str">
-        <v>MED-070</v>
-      </c>
-      <c r="D71" t="str">
+        <v>SMP064345-070</v>
+      </c>
+      <c r="D71">
         <v>30</v>
       </c>
       <c r="E71" t="str">
@@ -4340,7 +3925,7 @@
         <v>Injectables</v>
       </c>
       <c r="G71" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H71">
         <v>80.5</v>
@@ -4351,29 +3936,23 @@
       <c r="J71">
         <v>48</v>
       </c>
-      <c r="K71" t="str">
-        <v>8901100000070</v>
+      <c r="K71">
+        <v>89064345070</v>
       </c>
       <c r="L71" t="str">
-        <v>BCH-2026-070</v>
-      </c>
-      <c r="M71" t="str">
-        <v>2026-10-16</v>
-      </c>
-      <c r="N71" t="str">
-        <v>2029-10-19</v>
+        <v>B064345-070</v>
+      </c>
+      <c r="M71">
+        <v>46311.20847222222</v>
+      </c>
+      <c r="N71">
+        <v>47410.20847222222</v>
       </c>
       <c r="O71" t="str">
         <v>Abbott</v>
       </c>
       <c r="P71" t="str">
         <v>No</v>
-      </c>
-      <c r="Q71" t="str">
-        <v/>
-      </c>
-      <c r="R71" t="str">
-        <v/>
       </c>
     </row>
     <row r="72">
@@ -4384,9 +3963,9 @@
         <v>injection</v>
       </c>
       <c r="C72" t="str">
-        <v>MED-071</v>
-      </c>
-      <c r="D72" t="str">
+        <v>SMP064345-071</v>
+      </c>
+      <c r="D72">
         <v>10</v>
       </c>
       <c r="E72" t="str">
@@ -4396,7 +3975,7 @@
         <v>Analgesics</v>
       </c>
       <c r="G72" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H72">
         <v>80</v>
@@ -4407,29 +3986,23 @@
       <c r="J72">
         <v>50</v>
       </c>
-      <c r="K72" t="str">
-        <v>8901100000071</v>
+      <c r="K72">
+        <v>89064345071</v>
       </c>
       <c r="L72" t="str">
-        <v>BCH-2026-071</v>
-      </c>
-      <c r="M72" t="str">
-        <v>2025-11-17</v>
-      </c>
-      <c r="N72" t="str">
-        <v>2027-11-20</v>
+        <v>B064345-071</v>
+      </c>
+      <c r="M72">
+        <v>45978.20847222222</v>
+      </c>
+      <c r="N72">
+        <v>46711.20847222222</v>
       </c>
       <c r="O72" t="str">
         <v>Hilton</v>
       </c>
       <c r="P72" t="str">
         <v>No</v>
-      </c>
-      <c r="Q72" t="str">
-        <v/>
-      </c>
-      <c r="R72" t="str">
-        <v/>
       </c>
     </row>
     <row r="73">
@@ -4440,9 +4013,9 @@
         <v>injection</v>
       </c>
       <c r="C73" t="str">
-        <v>MED-072</v>
-      </c>
-      <c r="D73" t="str">
+        <v>SMP064345-072</v>
+      </c>
+      <c r="D73">
         <v>30</v>
       </c>
       <c r="E73" t="str">
@@ -4452,7 +4025,7 @@
         <v>Antibiotics</v>
       </c>
       <c r="G73" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H73">
         <v>83</v>
@@ -4463,29 +4036,23 @@
       <c r="J73">
         <v>52</v>
       </c>
-      <c r="K73" t="str">
-        <v>8901100000072</v>
+      <c r="K73">
+        <v>89064345072</v>
       </c>
       <c r="L73" t="str">
-        <v>BCH-2026-072</v>
-      </c>
-      <c r="M73" t="str">
-        <v>2026-12-18</v>
-      </c>
-      <c r="N73" t="str">
-        <v>2029-12-21</v>
+        <v>B064345-072</v>
+      </c>
+      <c r="M73">
+        <v>46374.20847222222</v>
+      </c>
+      <c r="N73">
+        <v>47473.20847222222</v>
       </c>
       <c r="O73" t="str">
         <v>Sami</v>
       </c>
       <c r="P73" t="str">
         <v>No</v>
-      </c>
-      <c r="Q73" t="str">
-        <v/>
-      </c>
-      <c r="R73" t="str">
-        <v/>
       </c>
     </row>
     <row r="74">
@@ -4496,9 +4063,9 @@
         <v>injection</v>
       </c>
       <c r="C74" t="str">
-        <v>MED-073</v>
-      </c>
-      <c r="D74" t="str">
+        <v>SMP064345-073</v>
+      </c>
+      <c r="D74">
         <v>75</v>
       </c>
       <c r="E74" t="str">
@@ -4508,7 +4075,7 @@
         <v>Antihistamines</v>
       </c>
       <c r="G74" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H74">
         <v>86</v>
@@ -4519,29 +4086,23 @@
       <c r="J74">
         <v>54</v>
       </c>
-      <c r="K74" t="str">
-        <v>8901100000073</v>
+      <c r="K74">
+        <v>89064345073</v>
       </c>
       <c r="L74" t="str">
-        <v>BCH-2026-073</v>
-      </c>
-      <c r="M74" t="str">
-        <v>2025-01-19</v>
-      </c>
-      <c r="N74" t="str">
-        <v>2027-01-22</v>
+        <v>B064345-073</v>
+      </c>
+      <c r="M74">
+        <v>45676.20847222222</v>
+      </c>
+      <c r="N74">
+        <v>46409.20847222222</v>
       </c>
       <c r="O74" t="str">
         <v>Highnoon</v>
       </c>
       <c r="P74" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q74" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R74">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="75">
@@ -4552,9 +4113,9 @@
         <v>injection</v>
       </c>
       <c r="C75" t="str">
-        <v>MED-074</v>
-      </c>
-      <c r="D75" t="str">
+        <v>SMP064345-074</v>
+      </c>
+      <c r="D75">
         <v>40</v>
       </c>
       <c r="E75" t="str">
@@ -4564,7 +4125,7 @@
         <v>Antacids</v>
       </c>
       <c r="G75" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H75">
         <v>89</v>
@@ -4575,29 +4136,23 @@
       <c r="J75">
         <v>56</v>
       </c>
-      <c r="K75" t="str">
-        <v>8901100000074</v>
+      <c r="K75">
+        <v>89064345074</v>
       </c>
       <c r="L75" t="str">
-        <v>BCH-2026-074</v>
-      </c>
-      <c r="M75" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="N75" t="str">
-        <v>2029-02-23</v>
+        <v>B064345-074</v>
+      </c>
+      <c r="M75">
+        <v>46073.20847222222</v>
+      </c>
+      <c r="N75">
+        <v>47172.20847222222</v>
       </c>
       <c r="O75" t="str">
         <v>Martin Dow</v>
       </c>
       <c r="P75" t="str">
         <v>No</v>
-      </c>
-      <c r="Q75" t="str">
-        <v/>
-      </c>
-      <c r="R75" t="str">
-        <v/>
       </c>
     </row>
     <row r="76">
@@ -4608,9 +4163,9 @@
         <v>injection</v>
       </c>
       <c r="C76" t="str">
-        <v>MED-075</v>
-      </c>
-      <c r="D76" t="str">
+        <v>SMP064345-075</v>
+      </c>
+      <c r="D76">
         <v>100</v>
       </c>
       <c r="E76" t="str">
@@ -4620,7 +4175,7 @@
         <v>Cardiovascular</v>
       </c>
       <c r="G76" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H76">
         <v>92</v>
@@ -4631,29 +4186,23 @@
       <c r="J76">
         <v>58</v>
       </c>
-      <c r="K76" t="str">
-        <v>8901100000075</v>
+      <c r="K76">
+        <v>89064345075</v>
       </c>
       <c r="L76" t="str">
-        <v>BCH-2026-075</v>
-      </c>
-      <c r="M76" t="str">
-        <v>2025-03-21</v>
-      </c>
-      <c r="N76" t="str">
-        <v>2027-03-24</v>
+        <v>B064345-075</v>
+      </c>
+      <c r="M76">
+        <v>45737.20847222222</v>
+      </c>
+      <c r="N76">
+        <v>46470.20847222222</v>
       </c>
       <c r="O76" t="str">
         <v>Pfizer</v>
       </c>
       <c r="P76" t="str">
         <v>No</v>
-      </c>
-      <c r="Q76" t="str">
-        <v/>
-      </c>
-      <c r="R76" t="str">
-        <v/>
       </c>
     </row>
     <row r="77">
@@ -4664,9 +4213,9 @@
         <v>injection</v>
       </c>
       <c r="C77" t="str">
-        <v>MED-076</v>
-      </c>
-      <c r="D77" t="str">
+        <v>SMP064345-076</v>
+      </c>
+      <c r="D77">
         <v>1</v>
       </c>
       <c r="E77" t="str">
@@ -4676,7 +4225,7 @@
         <v>Diabetes</v>
       </c>
       <c r="G77" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H77">
         <v>95</v>
@@ -4687,29 +4236,23 @@
       <c r="J77">
         <v>60</v>
       </c>
-      <c r="K77" t="str">
-        <v>8901100000076</v>
+      <c r="K77">
+        <v>89064345076</v>
       </c>
       <c r="L77" t="str">
-        <v>BCH-2026-076</v>
-      </c>
-      <c r="M77" t="str">
-        <v>2026-04-22</v>
-      </c>
-      <c r="N77" t="str">
-        <v>2029-04-25</v>
+        <v>B064345-076</v>
+      </c>
+      <c r="M77">
+        <v>46134.20847222222</v>
+      </c>
+      <c r="N77">
+        <v>47233.20847222222</v>
       </c>
       <c r="O77" t="str">
         <v>Novartis</v>
       </c>
       <c r="P77" t="str">
         <v>No</v>
-      </c>
-      <c r="Q77" t="str">
-        <v/>
-      </c>
-      <c r="R77" t="str">
-        <v/>
       </c>
     </row>
     <row r="78">
@@ -4720,9 +4263,9 @@
         <v>injection</v>
       </c>
       <c r="C78" t="str">
-        <v>MED-077</v>
-      </c>
-      <c r="D78" t="str">
+        <v>SMP064345-077</v>
+      </c>
+      <c r="D78">
         <v>1</v>
       </c>
       <c r="E78" t="str">
@@ -4732,7 +4275,7 @@
         <v>Vitamins</v>
       </c>
       <c r="G78" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H78">
         <v>98</v>
@@ -4743,29 +4286,23 @@
       <c r="J78">
         <v>62</v>
       </c>
-      <c r="K78" t="str">
-        <v>8901100000077</v>
+      <c r="K78">
+        <v>89064345077</v>
       </c>
       <c r="L78" t="str">
-        <v>BCH-2026-077</v>
-      </c>
-      <c r="M78" t="str">
-        <v>2025-05-23</v>
-      </c>
-      <c r="N78" t="str">
-        <v>2027-05-26</v>
+        <v>B064345-077</v>
+      </c>
+      <c r="M78">
+        <v>45800.20847222222</v>
+      </c>
+      <c r="N78">
+        <v>46533.20847222222</v>
       </c>
       <c r="O78" t="str">
         <v>Generic</v>
       </c>
       <c r="P78" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q78" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R78">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="79">
@@ -4776,9 +4313,9 @@
         <v>tablet</v>
       </c>
       <c r="C79" t="str">
-        <v>MED-078</v>
-      </c>
-      <c r="D79" t="str">
+        <v>SMP064345-078</v>
+      </c>
+      <c r="D79">
         <v>0.5</v>
       </c>
       <c r="E79" t="str">
@@ -4788,7 +4325,7 @@
         <v>Respiratory</v>
       </c>
       <c r="G79" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H79">
         <v>97.5</v>
@@ -4799,29 +4336,23 @@
       <c r="J79">
         <v>64</v>
       </c>
-      <c r="K79" t="str">
-        <v>8901100000078</v>
+      <c r="K79">
+        <v>89064345078</v>
       </c>
       <c r="L79" t="str">
-        <v>BCH-2026-078</v>
-      </c>
-      <c r="M79" t="str">
-        <v>2026-06-24</v>
-      </c>
-      <c r="N79" t="str">
-        <v>2029-06-27</v>
+        <v>B064345-078</v>
+      </c>
+      <c r="M79">
+        <v>46197.20847222222</v>
+      </c>
+      <c r="N79">
+        <v>47296.20847222222</v>
       </c>
       <c r="O79" t="str">
         <v>Getz</v>
       </c>
       <c r="P79" t="str">
         <v>No</v>
-      </c>
-      <c r="Q79" t="str">
-        <v/>
-      </c>
-      <c r="R79" t="str">
-        <v/>
       </c>
     </row>
     <row r="80">
@@ -4832,9 +4363,9 @@
         <v>tablet</v>
       </c>
       <c r="C80" t="str">
-        <v>MED-079</v>
-      </c>
-      <c r="D80" t="str">
+        <v>SMP064345-079</v>
+      </c>
+      <c r="D80">
         <v>20</v>
       </c>
       <c r="E80" t="str">
@@ -4844,7 +4375,7 @@
         <v>Dermatology</v>
       </c>
       <c r="G80" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H80">
         <v>100.5</v>
@@ -4855,29 +4386,23 @@
       <c r="J80">
         <v>66</v>
       </c>
-      <c r="K80" t="str">
-        <v>8901100000079</v>
+      <c r="K80">
+        <v>89064345079</v>
       </c>
       <c r="L80" t="str">
-        <v>BCH-2026-079</v>
-      </c>
-      <c r="M80" t="str">
-        <v>2025-07-25</v>
-      </c>
-      <c r="N80" t="str">
-        <v>2027-07-28</v>
+        <v>B064345-079</v>
+      </c>
+      <c r="M80">
+        <v>45863.20847222222</v>
+      </c>
+      <c r="N80">
+        <v>46596.20847222222</v>
       </c>
       <c r="O80" t="str">
         <v>Searle</v>
       </c>
       <c r="P80" t="str">
         <v>No</v>
-      </c>
-      <c r="Q80" t="str">
-        <v/>
-      </c>
-      <c r="R80" t="str">
-        <v/>
       </c>
     </row>
     <row r="81">
@@ -4888,9 +4413,9 @@
         <v>tablet</v>
       </c>
       <c r="C81" t="str">
-        <v>MED-080</v>
-      </c>
-      <c r="D81" t="str">
+        <v>SMP064345-080</v>
+      </c>
+      <c r="D81">
         <v>0.25</v>
       </c>
       <c r="E81" t="str">
@@ -4900,7 +4425,7 @@
         <v>Injectables</v>
       </c>
       <c r="G81" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H81">
         <v>103.5</v>
@@ -4911,29 +4436,23 @@
       <c r="J81">
         <v>68</v>
       </c>
-      <c r="K81" t="str">
-        <v>8901100000080</v>
+      <c r="K81">
+        <v>89064345080</v>
       </c>
       <c r="L81" t="str">
-        <v>BCH-2026-080</v>
-      </c>
-      <c r="M81" t="str">
-        <v>2026-08-26</v>
-      </c>
-      <c r="N81" t="str">
-        <v>2029-08-28</v>
+        <v>B064345-080</v>
+      </c>
+      <c r="M81">
+        <v>46260.20847222222</v>
+      </c>
+      <c r="N81">
+        <v>47358.20847222222</v>
       </c>
       <c r="O81" t="str">
         <v>GSK</v>
       </c>
       <c r="P81" t="str">
         <v>No</v>
-      </c>
-      <c r="Q81" t="str">
-        <v/>
-      </c>
-      <c r="R81" t="str">
-        <v/>
       </c>
     </row>
     <row r="82">
@@ -4944,9 +4463,9 @@
         <v>tablet</v>
       </c>
       <c r="C82" t="str">
-        <v>MED-081</v>
-      </c>
-      <c r="D82" t="str">
+        <v>SMP064345-081</v>
+      </c>
+      <c r="D82">
         <v>5</v>
       </c>
       <c r="E82" t="str">
@@ -4956,7 +4475,7 @@
         <v>Analgesics</v>
       </c>
       <c r="G82" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H82">
         <v>6.5</v>
@@ -4967,29 +4486,23 @@
       <c r="J82">
         <v>70</v>
       </c>
-      <c r="K82" t="str">
-        <v>8901100000081</v>
+      <c r="K82">
+        <v>89064345081</v>
       </c>
       <c r="L82" t="str">
-        <v>BCH-2026-081</v>
-      </c>
-      <c r="M82" t="str">
-        <v>2025-09-27</v>
-      </c>
-      <c r="N82" t="str">
-        <v>2027-09-28</v>
+        <v>B064345-081</v>
+      </c>
+      <c r="M82">
+        <v>45927.20847222222</v>
+      </c>
+      <c r="N82">
+        <v>46658.20847222222</v>
       </c>
       <c r="O82" t="str">
         <v>Abbott</v>
       </c>
       <c r="P82" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q82" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R82">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="83">
@@ -5000,9 +4513,9 @@
         <v>tablet</v>
       </c>
       <c r="C83" t="str">
-        <v>MED-082</v>
-      </c>
-      <c r="D83" t="str">
+        <v>SMP064345-082</v>
+      </c>
+      <c r="D83">
         <v>6.25</v>
       </c>
       <c r="E83" t="str">
@@ -5012,7 +4525,7 @@
         <v>Antibiotics</v>
       </c>
       <c r="G83" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H83">
         <v>9.5</v>
@@ -5023,29 +4536,23 @@
       <c r="J83">
         <v>72</v>
       </c>
-      <c r="K83" t="str">
-        <v>8901100000082</v>
+      <c r="K83">
+        <v>89064345082</v>
       </c>
       <c r="L83" t="str">
-        <v>BCH-2026-082</v>
-      </c>
-      <c r="M83" t="str">
-        <v>2026-10-01</v>
-      </c>
-      <c r="N83" t="str">
-        <v>2029-10-04</v>
+        <v>B064345-082</v>
+      </c>
+      <c r="M83">
+        <v>46296.20847222222</v>
+      </c>
+      <c r="N83">
+        <v>47395.20847222222</v>
       </c>
       <c r="O83" t="str">
         <v>Hilton</v>
       </c>
       <c r="P83" t="str">
         <v>No</v>
-      </c>
-      <c r="Q83" t="str">
-        <v/>
-      </c>
-      <c r="R83" t="str">
-        <v/>
       </c>
     </row>
     <row r="84">
@@ -5056,9 +4563,9 @@
         <v>tablet</v>
       </c>
       <c r="C84" t="str">
-        <v>MED-083</v>
-      </c>
-      <c r="D84" t="str">
+        <v>SMP064345-083</v>
+      </c>
+      <c r="D84">
         <v>5</v>
       </c>
       <c r="E84" t="str">
@@ -5068,7 +4575,7 @@
         <v>Antihistamines</v>
       </c>
       <c r="G84" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H84">
         <v>12.5</v>
@@ -5079,29 +4586,23 @@
       <c r="J84">
         <v>74</v>
       </c>
-      <c r="K84" t="str">
-        <v>8901100000083</v>
+      <c r="K84">
+        <v>89064345083</v>
       </c>
       <c r="L84" t="str">
-        <v>BCH-2026-083</v>
-      </c>
-      <c r="M84" t="str">
-        <v>2025-11-02</v>
-      </c>
-      <c r="N84" t="str">
-        <v>2027-11-05</v>
+        <v>B064345-083</v>
+      </c>
+      <c r="M84">
+        <v>45963.20847222222</v>
+      </c>
+      <c r="N84">
+        <v>46696.20847222222</v>
       </c>
       <c r="O84" t="str">
         <v>Sami</v>
       </c>
       <c r="P84" t="str">
         <v>No</v>
-      </c>
-      <c r="Q84" t="str">
-        <v/>
-      </c>
-      <c r="R84" t="str">
-        <v/>
       </c>
     </row>
     <row r="85">
@@ -5112,9 +4613,9 @@
         <v>tablet</v>
       </c>
       <c r="C85" t="str">
-        <v>MED-084</v>
-      </c>
-      <c r="D85" t="str">
+        <v>SMP064345-084</v>
+      </c>
+      <c r="D85">
         <v>5</v>
       </c>
       <c r="E85" t="str">
@@ -5124,7 +4625,7 @@
         <v>Antacids</v>
       </c>
       <c r="G85" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H85">
         <v>15.5</v>
@@ -5135,29 +4636,23 @@
       <c r="J85">
         <v>76</v>
       </c>
-      <c r="K85" t="str">
-        <v>8901100000084</v>
+      <c r="K85">
+        <v>89064345084</v>
       </c>
       <c r="L85" t="str">
-        <v>BCH-2026-084</v>
-      </c>
-      <c r="M85" t="str">
-        <v>2026-12-03</v>
-      </c>
-      <c r="N85" t="str">
-        <v>2029-12-06</v>
+        <v>B064345-084</v>
+      </c>
+      <c r="M85">
+        <v>46359.20847222222</v>
+      </c>
+      <c r="N85">
+        <v>47458.20847222222</v>
       </c>
       <c r="O85" t="str">
         <v>Highnoon</v>
       </c>
       <c r="P85" t="str">
         <v>No</v>
-      </c>
-      <c r="Q85" t="str">
-        <v/>
-      </c>
-      <c r="R85" t="str">
-        <v/>
       </c>
     </row>
     <row r="86">
@@ -5168,9 +4663,9 @@
         <v>tablet</v>
       </c>
       <c r="C86" t="str">
-        <v>MED-085</v>
-      </c>
-      <c r="D86" t="str">
+        <v>SMP064345-085</v>
+      </c>
+      <c r="D86">
         <v>40</v>
       </c>
       <c r="E86" t="str">
@@ -5180,7 +4675,7 @@
         <v>Cardiovascular</v>
       </c>
       <c r="G86" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H86">
         <v>15</v>
@@ -5191,29 +4686,23 @@
       <c r="J86">
         <v>78</v>
       </c>
-      <c r="K86" t="str">
-        <v>8901100000085</v>
+      <c r="K86">
+        <v>89064345085</v>
       </c>
       <c r="L86" t="str">
-        <v>BCH-2026-085</v>
-      </c>
-      <c r="M86" t="str">
-        <v>2025-01-04</v>
-      </c>
-      <c r="N86" t="str">
-        <v>2027-01-07</v>
+        <v>B064345-085</v>
+      </c>
+      <c r="M86">
+        <v>45661.20847222222</v>
+      </c>
+      <c r="N86">
+        <v>46394.20847222222</v>
       </c>
       <c r="O86" t="str">
         <v>Martin Dow</v>
       </c>
       <c r="P86" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q86" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R86">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="87">
@@ -5224,9 +4713,9 @@
         <v>tablet</v>
       </c>
       <c r="C87" t="str">
-        <v>MED-086</v>
-      </c>
-      <c r="D87" t="str">
+        <v>SMP064345-086</v>
+      </c>
+      <c r="D87">
         <v>80</v>
       </c>
       <c r="E87" t="str">
@@ -5236,7 +4725,7 @@
         <v>Diabetes</v>
       </c>
       <c r="G87" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H87">
         <v>18</v>
@@ -5247,29 +4736,23 @@
       <c r="J87">
         <v>80</v>
       </c>
-      <c r="K87" t="str">
-        <v>8901100000086</v>
+      <c r="K87">
+        <v>89064345086</v>
       </c>
       <c r="L87" t="str">
-        <v>BCH-2026-086</v>
-      </c>
-      <c r="M87" t="str">
-        <v>2026-02-05</v>
-      </c>
-      <c r="N87" t="str">
-        <v>2029-02-08</v>
+        <v>B064345-086</v>
+      </c>
+      <c r="M87">
+        <v>46058.20847222222</v>
+      </c>
+      <c r="N87">
+        <v>47157.20847222222</v>
       </c>
       <c r="O87" t="str">
         <v>Pfizer</v>
       </c>
       <c r="P87" t="str">
         <v>No</v>
-      </c>
-      <c r="Q87" t="str">
-        <v/>
-      </c>
-      <c r="R87" t="str">
-        <v/>
       </c>
     </row>
     <row r="88">
@@ -5280,9 +4763,9 @@
         <v>tablet</v>
       </c>
       <c r="C88" t="str">
-        <v>MED-087</v>
-      </c>
-      <c r="D88" t="str">
+        <v>SMP064345-087</v>
+      </c>
+      <c r="D88">
         <v>10</v>
       </c>
       <c r="E88" t="str">
@@ -5292,7 +4775,7 @@
         <v>Vitamins</v>
       </c>
       <c r="G88" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H88">
         <v>21</v>
@@ -5303,29 +4786,23 @@
       <c r="J88">
         <v>82</v>
       </c>
-      <c r="K88" t="str">
-        <v>8901100000087</v>
+      <c r="K88">
+        <v>89064345087</v>
       </c>
       <c r="L88" t="str">
-        <v>BCH-2026-087</v>
-      </c>
-      <c r="M88" t="str">
-        <v>2025-03-06</v>
-      </c>
-      <c r="N88" t="str">
-        <v>2027-03-09</v>
+        <v>B064345-087</v>
+      </c>
+      <c r="M88">
+        <v>45722.20847222222</v>
+      </c>
+      <c r="N88">
+        <v>46455.20847222222</v>
       </c>
       <c r="O88" t="str">
         <v>Novartis</v>
       </c>
       <c r="P88" t="str">
         <v>No</v>
-      </c>
-      <c r="Q88" t="str">
-        <v/>
-      </c>
-      <c r="R88" t="str">
-        <v/>
       </c>
     </row>
     <row r="89">
@@ -5336,9 +4813,9 @@
         <v>tablet</v>
       </c>
       <c r="C89" t="str">
-        <v>MED-088</v>
-      </c>
-      <c r="D89" t="str">
+        <v>SMP064345-088</v>
+      </c>
+      <c r="D89">
         <v>20</v>
       </c>
       <c r="E89" t="str">
@@ -5348,7 +4825,7 @@
         <v>Respiratory</v>
       </c>
       <c r="G89" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H89">
         <v>24</v>
@@ -5359,29 +4836,23 @@
       <c r="J89">
         <v>84</v>
       </c>
-      <c r="K89" t="str">
-        <v>8901100000088</v>
+      <c r="K89">
+        <v>89064345088</v>
       </c>
       <c r="L89" t="str">
-        <v>BCH-2026-088</v>
-      </c>
-      <c r="M89" t="str">
-        <v>2026-04-07</v>
-      </c>
-      <c r="N89" t="str">
-        <v>2029-04-10</v>
+        <v>B064345-088</v>
+      </c>
+      <c r="M89">
+        <v>46119.20847222222</v>
+      </c>
+      <c r="N89">
+        <v>47218.20847222222</v>
       </c>
       <c r="O89" t="str">
         <v>Generic</v>
       </c>
       <c r="P89" t="str">
         <v>No</v>
-      </c>
-      <c r="Q89" t="str">
-        <v/>
-      </c>
-      <c r="R89" t="str">
-        <v/>
       </c>
     </row>
     <row r="90">
@@ -5392,9 +4863,9 @@
         <v>capsule</v>
       </c>
       <c r="C90" t="str">
-        <v>MED-089</v>
-      </c>
-      <c r="D90" t="str">
+        <v>SMP064345-089</v>
+      </c>
+      <c r="D90">
         <v>200</v>
       </c>
       <c r="E90" t="str">
@@ -5404,7 +4875,7 @@
         <v>Dermatology</v>
       </c>
       <c r="G90" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H90">
         <v>27</v>
@@ -5415,29 +4886,23 @@
       <c r="J90">
         <v>86</v>
       </c>
-      <c r="K90" t="str">
-        <v>8901100000089</v>
+      <c r="K90">
+        <v>89064345089</v>
       </c>
       <c r="L90" t="str">
-        <v>BCH-2026-089</v>
-      </c>
-      <c r="M90" t="str">
-        <v>2025-05-08</v>
-      </c>
-      <c r="N90" t="str">
-        <v>2027-05-11</v>
+        <v>B064345-089</v>
+      </c>
+      <c r="M90">
+        <v>45785.20847222222</v>
+      </c>
+      <c r="N90">
+        <v>46518.20847222222</v>
       </c>
       <c r="O90" t="str">
         <v>Getz</v>
       </c>
       <c r="P90" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q90" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R90">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="91">
@@ -5448,9 +4913,9 @@
         <v>tablet</v>
       </c>
       <c r="C91" t="str">
-        <v>MED-090</v>
-      </c>
-      <c r="D91" t="str">
+        <v>SMP064345-090</v>
+      </c>
+      <c r="D91">
         <v>100</v>
       </c>
       <c r="E91" t="str">
@@ -5460,7 +4925,7 @@
         <v>Injectables</v>
       </c>
       <c r="G91" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H91">
         <v>30</v>
@@ -5471,29 +4936,23 @@
       <c r="J91">
         <v>88</v>
       </c>
-      <c r="K91" t="str">
-        <v>8901100000090</v>
+      <c r="K91">
+        <v>89064345090</v>
       </c>
       <c r="L91" t="str">
-        <v>BCH-2026-090</v>
-      </c>
-      <c r="M91" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="N91" t="str">
-        <v>2029-06-12</v>
+        <v>B064345-090</v>
+      </c>
+      <c r="M91">
+        <v>46182.20847222222</v>
+      </c>
+      <c r="N91">
+        <v>47281.20847222222</v>
       </c>
       <c r="O91" t="str">
         <v>Searle</v>
       </c>
       <c r="P91" t="str">
         <v>No</v>
-      </c>
-      <c r="Q91" t="str">
-        <v/>
-      </c>
-      <c r="R91" t="str">
-        <v/>
       </c>
     </row>
     <row r="92">
@@ -5504,9 +4963,9 @@
         <v>tablet</v>
       </c>
       <c r="C92" t="str">
-        <v>MED-091</v>
-      </c>
-      <c r="D92" t="str">
+        <v>SMP064345-091</v>
+      </c>
+      <c r="D92">
         <v>0.5</v>
       </c>
       <c r="E92" t="str">
@@ -5516,7 +4975,7 @@
         <v>Analgesics</v>
       </c>
       <c r="G92" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H92">
         <v>33</v>
@@ -5527,29 +4986,23 @@
       <c r="J92">
         <v>90</v>
       </c>
-      <c r="K92" t="str">
-        <v>8901100000091</v>
+      <c r="K92">
+        <v>89064345091</v>
       </c>
       <c r="L92" t="str">
-        <v>BCH-2026-091</v>
-      </c>
-      <c r="M92" t="str">
-        <v>2025-07-10</v>
-      </c>
-      <c r="N92" t="str">
-        <v>2027-07-13</v>
+        <v>B064345-091</v>
+      </c>
+      <c r="M92">
+        <v>45848.20847222222</v>
+      </c>
+      <c r="N92">
+        <v>46581.20847222222</v>
       </c>
       <c r="O92" t="str">
         <v>GSK</v>
       </c>
       <c r="P92" t="str">
         <v>No</v>
-      </c>
-      <c r="Q92" t="str">
-        <v/>
-      </c>
-      <c r="R92" t="str">
-        <v/>
       </c>
     </row>
     <row r="93">
@@ -5560,9 +5013,9 @@
         <v>tablet</v>
       </c>
       <c r="C93" t="str">
-        <v>MED-092</v>
-      </c>
-      <c r="D93" t="str">
+        <v>SMP064345-092</v>
+      </c>
+      <c r="D93">
         <v>2.5</v>
       </c>
       <c r="E93" t="str">
@@ -5572,7 +5025,7 @@
         <v>Antibiotics</v>
       </c>
       <c r="G93" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H93">
         <v>32.5</v>
@@ -5583,29 +5036,23 @@
       <c r="J93">
         <v>92</v>
       </c>
-      <c r="K93" t="str">
-        <v>8901100000092</v>
+      <c r="K93">
+        <v>89064345092</v>
       </c>
       <c r="L93" t="str">
-        <v>BCH-2026-092</v>
-      </c>
-      <c r="M93" t="str">
-        <v>2026-08-11</v>
-      </c>
-      <c r="N93" t="str">
-        <v>2029-08-14</v>
+        <v>B064345-092</v>
+      </c>
+      <c r="M93">
+        <v>46245.20847222222</v>
+      </c>
+      <c r="N93">
+        <v>47344.20847222222</v>
       </c>
       <c r="O93" t="str">
         <v>Abbott</v>
       </c>
       <c r="P93" t="str">
         <v>No</v>
-      </c>
-      <c r="Q93" t="str">
-        <v/>
-      </c>
-      <c r="R93" t="str">
-        <v/>
       </c>
     </row>
     <row r="94">
@@ -5616,9 +5063,9 @@
         <v>tablet</v>
       </c>
       <c r="C94" t="str">
-        <v>MED-093</v>
-      </c>
-      <c r="D94" t="str">
+        <v>SMP064345-093</v>
+      </c>
+      <c r="D94">
         <v>20</v>
       </c>
       <c r="E94" t="str">
@@ -5628,7 +5075,7 @@
         <v>Antihistamines</v>
       </c>
       <c r="G94" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H94">
         <v>35.5</v>
@@ -5639,29 +5086,23 @@
       <c r="J94">
         <v>94</v>
       </c>
-      <c r="K94" t="str">
-        <v>8901100000093</v>
+      <c r="K94">
+        <v>89064345093</v>
       </c>
       <c r="L94" t="str">
-        <v>BCH-2026-093</v>
-      </c>
-      <c r="M94" t="str">
-        <v>2025-09-12</v>
-      </c>
-      <c r="N94" t="str">
-        <v>2027-09-15</v>
+        <v>B064345-093</v>
+      </c>
+      <c r="M94">
+        <v>45912.20847222222</v>
+      </c>
+      <c r="N94">
+        <v>46645.20847222222</v>
       </c>
       <c r="O94" t="str">
         <v>Hilton</v>
       </c>
       <c r="P94" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q94" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R94">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="95">
@@ -5672,9 +5113,9 @@
         <v>capsule</v>
       </c>
       <c r="C95" t="str">
-        <v>MED-094</v>
-      </c>
-      <c r="D95" t="str">
+        <v>SMP064345-094</v>
+      </c>
+      <c r="D95">
         <v>0.4</v>
       </c>
       <c r="E95" t="str">
@@ -5684,7 +5125,7 @@
         <v>Antacids</v>
       </c>
       <c r="G95" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H95">
         <v>38.5</v>
@@ -5695,29 +5136,23 @@
       <c r="J95">
         <v>96</v>
       </c>
-      <c r="K95" t="str">
-        <v>8901100000094</v>
+      <c r="K95">
+        <v>89064345094</v>
       </c>
       <c r="L95" t="str">
-        <v>BCH-2026-094</v>
-      </c>
-      <c r="M95" t="str">
-        <v>2026-10-13</v>
-      </c>
-      <c r="N95" t="str">
-        <v>2029-10-16</v>
+        <v>B064345-094</v>
+      </c>
+      <c r="M95">
+        <v>46308.20847222222</v>
+      </c>
+      <c r="N95">
+        <v>47407.20847222222</v>
       </c>
       <c r="O95" t="str">
         <v>Sami</v>
       </c>
       <c r="P95" t="str">
         <v>No</v>
-      </c>
-      <c r="Q95" t="str">
-        <v/>
-      </c>
-      <c r="R95" t="str">
-        <v/>
       </c>
     </row>
     <row r="96">
@@ -5728,9 +5163,9 @@
         <v>tablet</v>
       </c>
       <c r="C96" t="str">
-        <v>MED-095</v>
-      </c>
-      <c r="D96" t="str">
+        <v>SMP064345-095</v>
+      </c>
+      <c r="D96">
         <v>5</v>
       </c>
       <c r="E96" t="str">
@@ -5740,7 +5175,7 @@
         <v>Cardiovascular</v>
       </c>
       <c r="G96" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H96">
         <v>41.5</v>
@@ -5751,29 +5186,23 @@
       <c r="J96">
         <v>98</v>
       </c>
-      <c r="K96" t="str">
-        <v>8901100000095</v>
+      <c r="K96">
+        <v>89064345095</v>
       </c>
       <c r="L96" t="str">
-        <v>BCH-2026-095</v>
-      </c>
-      <c r="M96" t="str">
-        <v>2025-11-14</v>
-      </c>
-      <c r="N96" t="str">
-        <v>2027-11-17</v>
+        <v>B064345-095</v>
+      </c>
+      <c r="M96">
+        <v>45975.20847222222</v>
+      </c>
+      <c r="N96">
+        <v>46708.20847222222</v>
       </c>
       <c r="O96" t="str">
         <v>Highnoon</v>
       </c>
       <c r="P96" t="str">
         <v>No</v>
-      </c>
-      <c r="Q96" t="str">
-        <v/>
-      </c>
-      <c r="R96" t="str">
-        <v/>
       </c>
     </row>
     <row r="97">
@@ -5784,9 +5213,9 @@
         <v>tablet</v>
       </c>
       <c r="C97" t="str">
-        <v>MED-096</v>
-      </c>
-      <c r="D97" t="str">
+        <v>SMP064345-096</v>
+      </c>
+      <c r="D97">
         <v>50</v>
       </c>
       <c r="E97" t="str">
@@ -5796,7 +5225,7 @@
         <v>Diabetes</v>
       </c>
       <c r="G97" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H97">
         <v>44.5</v>
@@ -5807,29 +5236,23 @@
       <c r="J97">
         <v>100</v>
       </c>
-      <c r="K97" t="str">
-        <v>8901100000096</v>
+      <c r="K97">
+        <v>89064345096</v>
       </c>
       <c r="L97" t="str">
-        <v>BCH-2026-096</v>
-      </c>
-      <c r="M97" t="str">
-        <v>2026-12-15</v>
-      </c>
-      <c r="N97" t="str">
-        <v>2029-12-18</v>
+        <v>B064345-096</v>
+      </c>
+      <c r="M97">
+        <v>46371.20847222222</v>
+      </c>
+      <c r="N97">
+        <v>47470.20847222222</v>
       </c>
       <c r="O97" t="str">
         <v>Martin Dow</v>
       </c>
       <c r="P97" t="str">
         <v>No</v>
-      </c>
-      <c r="Q97" t="str">
-        <v/>
-      </c>
-      <c r="R97" t="str">
-        <v/>
       </c>
     </row>
     <row r="98">
@@ -5840,9 +5263,9 @@
         <v>tablet</v>
       </c>
       <c r="C98" t="str">
-        <v>MED-097</v>
-      </c>
-      <c r="D98" t="str">
+        <v>SMP064345-097</v>
+      </c>
+      <c r="D98">
         <v>0.5</v>
       </c>
       <c r="E98" t="str">
@@ -5852,7 +5275,7 @@
         <v>Vitamins</v>
       </c>
       <c r="G98" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H98">
         <v>47.5</v>
@@ -5863,29 +5286,23 @@
       <c r="J98">
         <v>102</v>
       </c>
-      <c r="K98" t="str">
-        <v>8901100000097</v>
+      <c r="K98">
+        <v>89064345097</v>
       </c>
       <c r="L98" t="str">
-        <v>BCH-2026-097</v>
-      </c>
-      <c r="M98" t="str">
-        <v>2025-01-16</v>
-      </c>
-      <c r="N98" t="str">
-        <v>2027-01-19</v>
+        <v>B064345-097</v>
+      </c>
+      <c r="M98">
+        <v>45673.20847222222</v>
+      </c>
+      <c r="N98">
+        <v>46406.20847222222</v>
       </c>
       <c r="O98" t="str">
         <v>Pfizer</v>
       </c>
       <c r="P98" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="Q98" t="str">
-        <v>percentage</v>
-      </c>
-      <c r="R98">
-        <v>5</v>
+        <v>No</v>
       </c>
     </row>
     <row r="99">
@@ -5896,9 +5313,9 @@
         <v>tablet</v>
       </c>
       <c r="C99" t="str">
-        <v>MED-098</v>
-      </c>
-      <c r="D99" t="str">
+        <v>SMP064345-098</v>
+      </c>
+      <c r="D99">
         <v>50</v>
       </c>
       <c r="E99" t="str">
@@ -5908,7 +5325,7 @@
         <v>Respiratory</v>
       </c>
       <c r="G99" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H99">
         <v>50.5</v>
@@ -5919,29 +5336,23 @@
       <c r="J99">
         <v>104</v>
       </c>
-      <c r="K99" t="str">
-        <v>8901100000098</v>
+      <c r="K99">
+        <v>89064345098</v>
       </c>
       <c r="L99" t="str">
-        <v>BCH-2026-098</v>
-      </c>
-      <c r="M99" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="N99" t="str">
-        <v>2029-02-20</v>
+        <v>B064345-098</v>
+      </c>
+      <c r="M99">
+        <v>46070.20847222222</v>
+      </c>
+      <c r="N99">
+        <v>47169.20847222222</v>
       </c>
       <c r="O99" t="str">
         <v>Novartis</v>
       </c>
       <c r="P99" t="str">
         <v>No</v>
-      </c>
-      <c r="Q99" t="str">
-        <v/>
-      </c>
-      <c r="R99" t="str">
-        <v/>
       </c>
     </row>
     <row r="100">
@@ -5952,9 +5363,9 @@
         <v>tablet</v>
       </c>
       <c r="C100" t="str">
-        <v>MED-099</v>
-      </c>
-      <c r="D100" t="str">
+        <v>SMP064345-099</v>
+      </c>
+      <c r="D100">
         <v>10</v>
       </c>
       <c r="E100" t="str">
@@ -5964,7 +5375,7 @@
         <v>Dermatology</v>
       </c>
       <c r="G100" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H100">
         <v>50</v>
@@ -5975,29 +5386,23 @@
       <c r="J100">
         <v>106</v>
       </c>
-      <c r="K100" t="str">
-        <v>8901100000099</v>
+      <c r="K100">
+        <v>89064345099</v>
       </c>
       <c r="L100" t="str">
-        <v>BCH-2026-099</v>
-      </c>
-      <c r="M100" t="str">
-        <v>2025-03-18</v>
-      </c>
-      <c r="N100" t="str">
-        <v>2027-03-21</v>
+        <v>B064345-099</v>
+      </c>
+      <c r="M100">
+        <v>45734.20847222222</v>
+      </c>
+      <c r="N100">
+        <v>46467.20847222222</v>
       </c>
       <c r="O100" t="str">
         <v>Generic</v>
       </c>
       <c r="P100" t="str">
         <v>No</v>
-      </c>
-      <c r="Q100" t="str">
-        <v/>
-      </c>
-      <c r="R100" t="str">
-        <v/>
       </c>
     </row>
     <row r="101">
@@ -6008,9 +5413,9 @@
         <v>tablet</v>
       </c>
       <c r="C101" t="str">
-        <v>MED-100</v>
-      </c>
-      <c r="D101" t="str">
+        <v>SMP064345-100</v>
+      </c>
+      <c r="D101">
         <v>25</v>
       </c>
       <c r="E101" t="str">
@@ -6020,7 +5425,7 @@
         <v>Injectables</v>
       </c>
       <c r="G101" t="str">
-        <v>Main Pharmacy</v>
+        <v>Medicare Pharmacy Store</v>
       </c>
       <c r="H101">
         <v>53</v>
@@ -6031,29 +5436,23 @@
       <c r="J101">
         <v>108</v>
       </c>
-      <c r="K101" t="str">
-        <v>8901100000100</v>
+      <c r="K101">
+        <v>89064345100</v>
       </c>
       <c r="L101" t="str">
-        <v>BCH-2026-100</v>
-      </c>
-      <c r="M101" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="N101" t="str">
-        <v>2029-04-22</v>
+        <v>B064345-100</v>
+      </c>
+      <c r="M101">
+        <v>46131.20847222222</v>
+      </c>
+      <c r="N101">
+        <v>47230.20847222222</v>
       </c>
       <c r="O101" t="str">
         <v>Getz</v>
       </c>
       <c r="P101" t="str">
         <v>No</v>
-      </c>
-      <c r="Q101" t="str">
-        <v/>
-      </c>
-      <c r="R101" t="str">
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -6061,39 +5460,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:R101"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Topic</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Guidance</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Store</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Change Store * to your exact hospital store name</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Discount</v>
-      </c>
-      <c r="B3" t="str">
-        <v>If Discount Eligible=Yes, Max Discount Type + Max Discount Value are required</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
-  </ignoredErrors>
-</worksheet>
 </file>